--- a/samples/sample-records.xlsx
+++ b/samples/sample-records.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="353">
   <si>
     <t>Session ID</t>
   </si>
@@ -39,6 +39,15 @@
     <t>Location</t>
   </si>
   <si>
+    <t>GPS lat</t>
+  </si>
+  <si>
+    <t>GPS lon</t>
+  </si>
+  <si>
+    <t>Case / ref #</t>
+  </si>
+  <si>
     <t>Environment</t>
   </si>
   <si>
@@ -84,7 +93,7 @@
     <t>Reviewed by</t>
   </si>
   <si>
-    <t>0ba13948-8323-4d55-8e8e-2a6fd7c0ab26</t>
+    <t>1c34537e-6cd6-456b-957b-3cebf430d910</t>
   </si>
   <si>
     <t>08:30</t>
@@ -99,6 +108,9 @@
     <t>Fairview Training Annex</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>indoor</t>
   </si>
   <si>
@@ -120,16 +132,13 @@
     <t>Indoor, HVAC on</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>More elevated hides above chest height</t>
   </si>
   <si>
     <t>Completed</t>
   </si>
   <si>
-    <t>30d30988-1dc9-458f-8aca-865e9c8e01b7</t>
+    <t>22c36983-a5e0-4a01-94d3-844c35be481e</t>
   </si>
   <si>
     <t>17:15</t>
@@ -165,7 +174,7 @@
     <t>Lt. C. Barnes</t>
   </si>
   <si>
-    <t>ac6a7b83-6b0d-4cf7-9f02-bf2465a57a9d</t>
+    <t>939b5190-a131-4843-9c4e-2dca8db97b40</t>
   </si>
   <si>
     <t>09:00</t>
@@ -195,7 +204,7 @@
     <t>Maintain double-blind cadence monthly</t>
   </si>
   <si>
-    <t>000db8fe-1e79-4bb1-9674-176b1b436e9d</t>
+    <t>f0c810eb-f036-4968-aa6f-538fb32c82c5</t>
   </si>
   <si>
     <t>07:45</t>
@@ -219,7 +228,7 @@
     <t>Overcast, wind 5-10 mph from west</t>
   </si>
   <si>
-    <t>f038f10c-f1f2-45be-b55b-15f932a6e125</t>
+    <t>0d8bb97c-e8a0-4d01-b667-8fcf1d9ae789</t>
   </si>
   <si>
     <t>13:00</t>
@@ -240,7 +249,7 @@
     <t>Increase parcel line length; add moving-belt scenario when available</t>
   </si>
   <si>
-    <t>9a40fb5a-d782-4b5c-b313-25d274347898</t>
+    <t>78b22f1d-daa6-484a-9760-1b2c33421082</t>
   </si>
   <si>
     <t>10:00</t>
@@ -267,7 +276,7 @@
     <t>Schedule monthly shoreline maintenance; work under-deck airflow problems</t>
   </si>
   <si>
-    <t>899122cc-20ff-451e-9a01-4c1152532e15</t>
+    <t>ebf5ba77-6e92-4668-ab00-b077fe48be39</t>
   </si>
   <si>
     <t>08:15</t>
@@ -282,7 +291,7 @@
     <t>High-clutter environment with shelving to 12 ft. Cooper maintained drive throughout a long problem. Elevated SSD at 6 ft found via air scent cone. One false response near a shelf of seized electronics equipment (actual odor source plausible — logged as unconfirmed rather than false).</t>
   </si>
   <si>
-    <t>1f2bdd51-1a96-4800-a484-cf68681ccab8</t>
+    <t>f608810e-df97-4c23-9cb6-bbda84773561</t>
   </si>
   <si>
     <t>09:30</t>
@@ -390,45 +399,75 @@
     <t>Comments</t>
   </si>
   <si>
-    <t>0162049c-f461-4ad9-9fb7-8729c80fc23b</t>
+    <t>075d520b-9f13-4237-849e-1b1f0928f631</t>
+  </si>
+  <si>
+    <t>Room / building search</t>
+  </si>
+  <si>
+    <t>Office</t>
+  </si>
+  <si>
+    <t>Single-blind</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Three connected offices, second floor</t>
+  </si>
+  <si>
+    <t>Sit (passive)</t>
+  </si>
+  <si>
+    <t>food</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>successful</t>
+  </si>
+  <si>
+    <t>24ba8f0f-63c0-4110-b068-136e3581bce9</t>
+  </si>
+  <si>
+    <t>Water / shoreline</t>
+  </si>
+  <si>
+    <t>Known hide</t>
+  </si>
+  <si>
+    <t>Dock and shoreline, ~80 yards</t>
+  </si>
+  <si>
+    <t>needs_work</t>
+  </si>
+  <si>
+    <t>Onshore wind pushed odor under decking; discussed presentation options.</t>
+  </si>
+  <si>
+    <t>86c79adf-8fdd-4524-84c4-1143a57beec0</t>
   </si>
   <si>
     <t>Training boxes</t>
   </si>
   <si>
-    <t>Known hide</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>12-box line, one hot box</t>
   </si>
   <si>
-    <t>Sit (passive)</t>
-  </si>
-  <si>
-    <t>food</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>successful</t>
-  </si>
-  <si>
-    <t>208009d2-8f93-4ac1-a0fb-3cb035f7686a</t>
+    <t>9d14f059-7739-4904-8b66-77ea53ef1627</t>
+  </si>
+  <si>
+    <t>12-box line, six hot boxes run sequentially</t>
+  </si>
+  <si>
+    <t>b14fdb3f-3a1a-4f5b-8f62-7cef7224606c</t>
   </si>
   <si>
     <t>Blank / negative search</t>
   </si>
   <si>
-    <t>Office</t>
-  </si>
-  <si>
-    <t>Single-blind</t>
-  </si>
-  <si>
     <t>Correct (clear)</t>
   </si>
   <si>
@@ -438,7 +477,43 @@
     <t>Clean blank. No interest shown, handler called the room clear.</t>
   </si>
   <si>
-    <t>29ec7174-1221-4eb0-9a1b-155fb98a8ce0</t>
+    <t>b33e0638-0cdf-49d2-8501-dbb14a82726a</t>
+  </si>
+  <si>
+    <t>Cluttered environment</t>
+  </si>
+  <si>
+    <t>Warehouse</t>
+  </si>
+  <si>
+    <t>Warehouse floor, aisles A-D</t>
+  </si>
+  <si>
+    <t>db330657-7c1e-4d7e-a868-5ac8020ee662</t>
+  </si>
+  <si>
+    <t>Vehicle search</t>
+  </si>
+  <si>
+    <t>Four sedans, parking level 1</t>
+  </si>
+  <si>
+    <t>Heat affected later runs; added rest and water breaks between vehicles.</t>
+  </si>
+  <si>
+    <t>eaead4ef-2765-4155-b46e-14a1d575d146</t>
+  </si>
+  <si>
+    <t>Outdoor / open area</t>
+  </si>
+  <si>
+    <t>Tree line and picnic area, ~100 x 40 yards</t>
+  </si>
+  <si>
+    <t>Worked crosswind pattern; off-leash under voice control.</t>
+  </si>
+  <si>
+    <t>ee3a38cc-f66b-4c43-9bf1-18e38757da4e</t>
   </si>
   <si>
     <t>Parcel / luggage / mail</t>
@@ -450,43 +525,7 @@
     <t>Distractors: sealed food, cables, charger. Correct discrimination throughout.</t>
   </si>
   <si>
-    <t>36fff9f7-2471-4a52-baea-3093104294b5</t>
-  </si>
-  <si>
-    <t>Outdoor / open area</t>
-  </si>
-  <si>
-    <t>Tree line and picnic area, ~100 x 40 yards</t>
-  </si>
-  <si>
-    <t>Worked crosswind pattern; off-leash under voice control.</t>
-  </si>
-  <si>
-    <t>80f57ccc-4d06-4236-978b-00ed624e4cb5</t>
-  </si>
-  <si>
-    <t>Water / shoreline</t>
-  </si>
-  <si>
-    <t>Dock and shoreline, ~80 yards</t>
-  </si>
-  <si>
-    <t>needs_work</t>
-  </si>
-  <si>
-    <t>Onshore wind pushed odor under decking; discussed presentation options.</t>
-  </si>
-  <si>
-    <t>ae6b0908-2a1a-45c1-9238-d1601ed3b4a9</t>
-  </si>
-  <si>
-    <t>12-box line, six hot boxes run sequentially</t>
-  </si>
-  <si>
-    <t>af8fdc24-7417-4e7c-863f-ad40b6de4be6</t>
-  </si>
-  <si>
-    <t>Room / building search</t>
+    <t>fdbf140d-dea5-4e43-b360-50eb2da880b6</t>
   </si>
   <si>
     <t>School / classroom</t>
@@ -501,36 +540,6 @@
     <t>Evaluator scored the run; handler had no knowledge of placements.</t>
   </si>
   <si>
-    <t>d18f2621-38f6-4775-bfe9-e0210b697e7a</t>
-  </si>
-  <si>
-    <t>Vehicle search</t>
-  </si>
-  <si>
-    <t>Four sedans, parking level 1</t>
-  </si>
-  <si>
-    <t>Heat affected later runs; added rest and water breaks between vehicles.</t>
-  </si>
-  <si>
-    <t>db1ce817-6d32-4d3b-b9aa-420189225fa0</t>
-  </si>
-  <si>
-    <t>Three connected offices, second floor</t>
-  </si>
-  <si>
-    <t>f5337d66-cc6e-439b-bc90-05e1c891ef30</t>
-  </si>
-  <si>
-    <t>Cluttered environment</t>
-  </si>
-  <si>
-    <t>Warehouse</t>
-  </si>
-  <si>
-    <t>Warehouse floor, aisles A-D</t>
-  </si>
-  <si>
     <t>Hide ID</t>
   </si>
   <si>
@@ -579,7 +588,7 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>023baae9-7f51-4356-955d-8c9d687ca0e0</t>
+    <t>05ed2830-029c-452f-93c6-db70e3a33fff</t>
   </si>
   <si>
     <t>Electronic storage device</t>
@@ -588,61 +597,238 @@
     <t>USB drive</t>
   </si>
   <si>
+    <t>Taped under dock decking, mid-span</t>
+  </si>
+  <si>
+    <t>floor</t>
+  </si>
+  <si>
+    <t>fully concealed</t>
+  </si>
+  <si>
+    <t>Found — handler assisted</t>
+  </si>
+  <si>
+    <t>Directed recheck after first pass; correct response on presentation</t>
+  </si>
+  <si>
+    <t>0d0bf1c5-917f-4462-8dc9-00574a8b48be</t>
+  </si>
+  <si>
+    <t>SD card</t>
+  </si>
+  <si>
+    <t>Box 5</t>
+  </si>
+  <si>
+    <t>Found — independent</t>
+  </si>
+  <si>
+    <t>105bb7eb-6b03-431a-870b-829f51ff43af</t>
+  </si>
+  <si>
+    <t>Tablet</t>
+  </si>
+  <si>
+    <t>Teacher lounge, locker 12</t>
+  </si>
+  <si>
+    <t>chest</t>
+  </si>
+  <si>
+    <t>Missed</t>
+  </si>
+  <si>
+    <t>Locker vents faced away from aisle; airflow discussed with evaluator</t>
+  </si>
+  <si>
+    <t>16abf7ba-9ab5-45b0-9be3-817a903ec215</t>
+  </si>
+  <si>
+    <t>SIM card</t>
+  </si>
+  <si>
+    <t>Magnet box, rear wheel well, vehicle 3</t>
+  </si>
+  <si>
+    <t>knee</t>
+  </si>
+  <si>
+    <t>Missed on first pass; found on re-run with handler presenting the wheel well</t>
+  </si>
+  <si>
+    <t>2089b8bf-7329-464b-97cb-aa777434e3de</t>
+  </si>
+  <si>
+    <t>Box 11</t>
+  </si>
+  <si>
+    <t>229490a4-9040-4184-aaeb-3307c8a88109</t>
+  </si>
+  <si>
+    <t>MicroSD card</t>
+  </si>
+  <si>
+    <t>Box 8</t>
+  </si>
+  <si>
+    <t>37793846-4bd7-41bf-9c2c-e41d2d9d6efb</t>
+  </si>
+  <si>
+    <t>Hard drive</t>
+  </si>
+  <si>
+    <t>Library AV closet, top shelf</t>
+  </si>
+  <si>
+    <t>elevated</t>
+  </si>
+  <si>
+    <t>partially concealed</t>
+  </si>
+  <si>
+    <t>Elevated hide — good air scenting</t>
+  </si>
+  <si>
+    <t>459809df-f05d-4f50-9d79-c46802b4f87c</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>Aisle B, shelf at ~6 ft</t>
+  </si>
+  <si>
+    <t>4bd8b650-373e-4322-a0b7-41ed157aee22</t>
+  </si>
+  <si>
+    <t>Cellphone</t>
+  </si>
+  <si>
+    <t>Parcel 9 (residual — phone removed prior day)</t>
+  </si>
+  <si>
+    <t>Interest, no indication</t>
+  </si>
+  <si>
+    <t>Interest only, no final response; treated as correct discrimination of residual odor</t>
+  </si>
+  <si>
+    <t>4e465b85-899c-49cf-b1f5-087b3fa03ee9</t>
+  </si>
+  <si>
+    <t>Parcel 6, wrapped in clothing</t>
+  </si>
+  <si>
+    <t>6232cdfb-edf6-40fe-8a74-871f2a26bd28</t>
+  </si>
+  <si>
+    <t>Pill bottle inside toolbox, aisle A</t>
+  </si>
+  <si>
+    <t>waist</t>
+  </si>
+  <si>
+    <t>6404447e-8e5a-47b0-9faf-65040d768772</t>
+  </si>
+  <si>
+    <t>Desk drawer, second from top</t>
+  </si>
+  <si>
+    <t>6cb163f3-a5c9-421f-b4dc-9d4517ed38b9</t>
+  </si>
+  <si>
+    <t>Classroom 3, bookshelf, third shelf</t>
+  </si>
+  <si>
+    <t>75034a3f-e137-4171-a366-d5ced551169d</t>
+  </si>
+  <si>
+    <t>Box 9 (second run)</t>
+  </si>
+  <si>
+    <t>76f6e59e-30d2-41ff-a926-a161e4e8ed2d</t>
+  </si>
+  <si>
+    <t>Classroom 4, pencil box in desk</t>
+  </si>
+  <si>
+    <t>77c613b1-d684-4446-9e35-2c8e5d8c5e8e</t>
+  </si>
+  <si>
+    <t>Parcel 14, inside greeting card</t>
+  </si>
+  <si>
+    <t>790245ae-1b44-44f6-a389-c789576a9101</t>
+  </si>
+  <si>
+    <t>Parcel 21, boxed with packing foam</t>
+  </si>
+  <si>
+    <t>7f399786-9f9f-4446-b1a2-0224a87d6e7a</t>
+  </si>
+  <si>
+    <t>Under driver seat, vehicle 1</t>
+  </si>
+  <si>
+    <t>88c9fd69-f9aa-439e-a88f-fc789b2d1b41</t>
+  </si>
+  <si>
     <t>Box 7 of 12</t>
   </si>
   <si>
-    <t>fully concealed</t>
-  </si>
-  <si>
-    <t>Found — independent</t>
-  </si>
-  <si>
-    <t>064656b9-41d4-4840-b360-6d9d136754d4</t>
-  </si>
-  <si>
-    <t>Tablet</t>
-  </si>
-  <si>
-    <t>Teacher lounge, locker 12</t>
-  </si>
-  <si>
-    <t>chest</t>
-  </si>
-  <si>
-    <t>Missed</t>
-  </si>
-  <si>
-    <t>Locker vents faced away from aisle; airflow discussed with evaluator</t>
-  </si>
-  <si>
-    <t>2af77ecf-f3dc-4f52-82cf-d566290ed449</t>
-  </si>
-  <si>
-    <t>Taped under dock decking, mid-span</t>
-  </si>
-  <si>
-    <t>floor</t>
-  </si>
-  <si>
-    <t>Found — handler assisted</t>
-  </si>
-  <si>
-    <t>Directed recheck after first pass; correct response on presentation</t>
-  </si>
-  <si>
-    <t>2dcce158-ff52-4f65-9078-5dc259967ace</t>
-  </si>
-  <si>
-    <t>MicroSD card</t>
-  </si>
-  <si>
-    <t>Pill bottle inside toolbox, aisle A</t>
-  </si>
-  <si>
-    <t>waist</t>
-  </si>
-  <si>
-    <t>333f77b0-3efa-4cde-ac72-703e779801f7</t>
+    <t>9964ece3-92ab-4b79-af44-5ebd42044fe7</t>
+  </si>
+  <si>
+    <t>Classroom 5, taped under chair</t>
+  </si>
+  <si>
+    <t>a36502d5-84b0-44a8-8f51-a606b37e4dfa</t>
+  </si>
+  <si>
+    <t>Library, inside hollowed book</t>
+  </si>
+  <si>
+    <t>a786eea6-e619-4630-b850-a9ca0286f544</t>
+  </si>
+  <si>
+    <t>Inside rolled carpet, aisle D</t>
+  </si>
+  <si>
+    <t>c53c6500-17ce-4931-8833-acd27e17b544</t>
+  </si>
+  <si>
+    <t>Dry bag at waterline piling</t>
+  </si>
+  <si>
+    <t>dcb0438f-12ba-4185-bbdd-339d1736db87</t>
+  </si>
+  <si>
+    <t>Glove box, vehicle 4</t>
+  </si>
+  <si>
+    <t>e28b04be-7247-4eae-a4a5-401d168e9ccf</t>
+  </si>
+  <si>
+    <t>Box 2</t>
+  </si>
+  <si>
+    <t>e426f2d9-4174-410b-8c07-ab49975a35b6</t>
+  </si>
+  <si>
+    <t>Box 3 (second run)</t>
+  </si>
+  <si>
+    <t>ebde832a-8822-495b-84d6-6b5c03fcd7c3</t>
+  </si>
+  <si>
+    <t>Behind loose baseboard, north wall</t>
+  </si>
+  <si>
+    <t>Required second pass; committed final response, no cue given</t>
+  </si>
+  <si>
+    <t>fa044aec-bbb2-42bf-9c6f-e62bc4d5da28</t>
   </si>
   <si>
     <t>Buried ~4 in. at base of oak, marked GPS</t>
@@ -651,189 +837,12 @@
     <t>buried</t>
   </si>
   <si>
-    <t>43250004-b011-4f19-9307-4a4ca86bf4c3</t>
-  </si>
-  <si>
-    <t>SIM card</t>
-  </si>
-  <si>
-    <t>Magnet box, rear wheel well, vehicle 3</t>
-  </si>
-  <si>
-    <t>knee</t>
-  </si>
-  <si>
-    <t>Missed on first pass; found on re-run with handler presenting the wheel well</t>
-  </si>
-  <si>
-    <t>4c4f9f87-4ab8-45d7-8b6b-e6de61fea17c</t>
-  </si>
-  <si>
-    <t>Cellphone</t>
-  </si>
-  <si>
-    <t>Classroom 3, bookshelf, third shelf</t>
-  </si>
-  <si>
-    <t>partially concealed</t>
-  </si>
-  <si>
-    <t>5d3da643-2012-45e3-9c5e-e24bf62caa41</t>
-  </si>
-  <si>
-    <t>Hard drive</t>
-  </si>
-  <si>
-    <t>Library AV closet, top shelf</t>
-  </si>
-  <si>
-    <t>elevated</t>
-  </si>
-  <si>
-    <t>Elevated hide — good air scenting</t>
-  </si>
-  <si>
-    <t>624841bf-72e1-45ee-99ab-100e2e800f61</t>
-  </si>
-  <si>
-    <t>SSD</t>
-  </si>
-  <si>
-    <t>Aisle B, shelf at ~6 ft</t>
-  </si>
-  <si>
-    <t>63bb9e28-0090-4280-a420-71a12ac6ea30</t>
-  </si>
-  <si>
-    <t>Box 8</t>
-  </si>
-  <si>
-    <t>687759a2-abb0-4749-ae0a-30215b1d217e</t>
-  </si>
-  <si>
-    <t>Box 2</t>
-  </si>
-  <si>
-    <t>69daa863-8e08-44c3-9c9f-65d5d99985fa</t>
-  </si>
-  <si>
-    <t>Parcel 21, boxed with packing foam</t>
-  </si>
-  <si>
-    <t>7b730ce6-378d-41b6-86dc-9d818c12e18a</t>
-  </si>
-  <si>
-    <t>Classroom 4, pencil box in desk</t>
-  </si>
-  <si>
-    <t>8253b3c3-0f0d-4d82-8f3f-7511232aec60</t>
-  </si>
-  <si>
-    <t>Inside rolled carpet, aisle D</t>
-  </si>
-  <si>
-    <t>83362a14-616c-4fbe-b43f-8619b3371684</t>
-  </si>
-  <si>
-    <t>Box 9 (second run)</t>
-  </si>
-  <si>
-    <t>8a09ca30-5349-4f32-9512-3cfd5ec93d20</t>
-  </si>
-  <si>
-    <t>Library, inside hollowed book</t>
-  </si>
-  <si>
-    <t>911ece0e-5ddc-4cfe-bb33-1f11009ea709</t>
-  </si>
-  <si>
-    <t>Box 3 (second run)</t>
-  </si>
-  <si>
-    <t>93a8767a-f265-4c62-95a0-6cfba7865e68</t>
-  </si>
-  <si>
-    <t>Behind loose baseboard, north wall</t>
-  </si>
-  <si>
-    <t>Required second pass; committed final response, no cue given</t>
-  </si>
-  <si>
-    <t>995ec416-3087-4ca6-8492-b9f1e876596f</t>
-  </si>
-  <si>
-    <t>Dry bag at waterline piling</t>
-  </si>
-  <si>
-    <t>b780cd9a-abbd-448c-b53f-704a010b5306</t>
+    <t>fb6c08c6-82cb-4e9e-874f-046636d6db89</t>
   </si>
   <si>
     <t>Under park bench slat</t>
   </si>
   <si>
-    <t>c01c2160-8cb4-4ec6-8884-3cb0fa7736ea</t>
-  </si>
-  <si>
-    <t>Under driver seat, vehicle 1</t>
-  </si>
-  <si>
-    <t>c2215c27-92d8-4a38-af5c-b4ec246fe285</t>
-  </si>
-  <si>
-    <t>SD card</t>
-  </si>
-  <si>
-    <t>Parcel 14, inside greeting card</t>
-  </si>
-  <si>
-    <t>cd03f52c-eade-4756-a1ec-f0990d46bc16</t>
-  </si>
-  <si>
-    <t>Parcel 9 (residual — phone removed prior day)</t>
-  </si>
-  <si>
-    <t>Interest, no indication</t>
-  </si>
-  <si>
-    <t>Interest only, no final response; treated as correct discrimination of residual odor</t>
-  </si>
-  <si>
-    <t>d1e5466a-01c6-4591-addc-8e9e1d0140dc</t>
-  </si>
-  <si>
-    <t>Box 11</t>
-  </si>
-  <si>
-    <t>df3b62fb-49a8-466b-b5bf-7d7728199c0d</t>
-  </si>
-  <si>
-    <t>Parcel 6, wrapped in clothing</t>
-  </si>
-  <si>
-    <t>dffd7ee8-4cd4-45c8-8b46-c6e640d17cec</t>
-  </si>
-  <si>
-    <t>Classroom 5, taped under chair</t>
-  </si>
-  <si>
-    <t>e0708c35-b754-4ed7-ad43-2cd05c530943</t>
-  </si>
-  <si>
-    <t>Desk drawer, second from top</t>
-  </si>
-  <si>
-    <t>e88bf050-1da3-4a4d-9227-dee84d3150fc</t>
-  </si>
-  <si>
-    <t>Box 5</t>
-  </si>
-  <si>
-    <t>ece9ebd1-eb6b-4937-a222-c5d9f60cc7ad</t>
-  </si>
-  <si>
-    <t>Glove box, vehicle 4</t>
-  </si>
-  <si>
     <t>Outcome category</t>
   </si>
   <si>
@@ -849,12 +858,12 @@
     <t>False response</t>
   </si>
   <si>
+    <t>Aisle C, shelf of seized AV equipment — suspected cause: Unconfirmed — possible actual storage media within sealed evidence; could not verify</t>
+  </si>
+  <si>
     <t>Cafeteria storage cabinet — suspected cause: Suspected residual odor — cabinet previously stored tablets</t>
   </si>
   <si>
-    <t>Aisle C, shelf of seized AV equipment — suspected cause: Unconfirmed — possible actual storage media within sealed evidence; could not verify</t>
-  </si>
-  <si>
     <t>Metric</t>
   </si>
   <si>
@@ -954,58 +963,58 @@
     <t>By search type</t>
   </si>
   <si>
+    <t xml:space="preserve">  Room / building search</t>
+  </si>
+  <si>
+    <t>2 exercises</t>
+  </si>
+  <si>
+    <t>8 hides, 7 finds, 1 misses. Last practiced 2026-08-14.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Water / shoreline</t>
+  </si>
+  <si>
+    <t>1 exercises</t>
+  </si>
+  <si>
+    <t>2 hides, 2 finds, 0 misses. Last practiced 2026-07-27.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  Training boxes</t>
   </si>
   <si>
-    <t>2 exercises</t>
-  </si>
-  <si>
     <t>7 hides, 7 finds, 0 misses. Last practiced 2026-08-14.</t>
   </si>
   <si>
     <t xml:space="preserve">  Blank / negative search</t>
   </si>
   <si>
-    <t>1 exercises</t>
-  </si>
-  <si>
     <t>0 hides, 0 finds, 0 misses. Last practiced 2026-08-14.</t>
   </si>
   <si>
+    <t xml:space="preserve">  Cluttered environment</t>
+  </si>
+  <si>
+    <t>3 hides, 3 finds, 0 misses. Last practiced 2026-07-20.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Vehicle search</t>
+  </si>
+  <si>
+    <t>3 hides, 2 finds, 1 misses. Last practiced 2026-08-11.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Outdoor / open area</t>
+  </si>
+  <si>
+    <t>2 hides, 2 finds, 0 misses. Last practiced 2026-08-04.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  Parcel / luggage / mail</t>
   </si>
   <si>
     <t>4 hides, 3 finds, 0 misses. Last practiced 2026-07-31.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Outdoor / open area</t>
-  </si>
-  <si>
-    <t>2 hides, 2 finds, 0 misses. Last practiced 2026-08-04.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Water / shoreline</t>
-  </si>
-  <si>
-    <t>2 hides, 2 finds, 0 misses. Last practiced 2026-07-27.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Room / building search</t>
-  </si>
-  <si>
-    <t>8 hides, 7 finds, 1 misses. Last practiced 2026-08-14.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Vehicle search</t>
-  </si>
-  <si>
-    <t>3 hides, 2 finds, 1 misses. Last practiced 2026-08-11.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Cluttered environment</t>
-  </si>
-  <si>
-    <t>3 hides, 3 finds, 0 misses. Last practiced 2026-07-20.</t>
   </si>
   <si>
     <t>Sheet</t>
@@ -1471,7 +1480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1480,23 +1489,25 @@
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
-    <col min="12" max="12" width="40" customWidth="1"/>
-    <col min="13" max="13" width="60" customWidth="1"/>
-    <col min="14" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="10" customWidth="1"/>
-    <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="40" customWidth="1"/>
-    <col min="18" max="18" width="30" customWidth="1"/>
-    <col min="19" max="19" width="12" customWidth="1"/>
-    <col min="20" max="21" width="18" style="2" customWidth="1"/>
-    <col min="22" max="22" width="18" customWidth="1"/>
+    <col min="8" max="9" width="11" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="15" max="15" width="40" customWidth="1"/>
+    <col min="16" max="16" width="60" customWidth="1"/>
+    <col min="17" max="17" width="12" customWidth="1"/>
+    <col min="18" max="18" width="10" customWidth="1"/>
+    <col min="19" max="19" width="18" customWidth="1"/>
+    <col min="20" max="20" width="40" customWidth="1"/>
+    <col min="21" max="21" width="30" customWidth="1"/>
+    <col min="22" max="22" width="12" customWidth="1"/>
+    <col min="23" max="24" width="18" style="2" customWidth="1"/>
+    <col min="25" max="25" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1554,562 +1565,643 @@
       <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
       <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B2" s="1">
         <v>46248.29166666667</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E2">
         <v>95</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2">
+        <v>33</v>
+      </c>
+      <c r="N2" t="s">
+        <v>34</v>
+      </c>
+      <c r="O2" t="s">
+        <v>35</v>
+      </c>
+      <c r="P2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q2">
         <v>4</v>
       </c>
-      <c r="O2">
+      <c r="R2">
         <v>72</v>
       </c>
-      <c r="P2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R2" t="s">
-        <v>35</v>
-      </c>
       <c r="S2" t="s">
-        <v>36</v>
-      </c>
-      <c r="T2" s="2">
-        <v>46251.18249303241</v>
-      </c>
-      <c r="U2" s="2">
-        <v>46251.18249303241</v>
+        <v>37</v>
+      </c>
+      <c r="T2" t="s">
+        <v>30</v>
+      </c>
+      <c r="U2" t="s">
+        <v>38</v>
       </c>
       <c r="V2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="W2" s="2">
+        <v>46251.19757380787</v>
+      </c>
+      <c r="X2" s="2">
+        <v>46251.19757380787</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B3" s="1">
         <v>46245.29166666667</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E3">
         <v>65</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H3" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="I3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K3" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="M3" t="s">
-        <v>43</v>
-      </c>
-      <c r="N3">
+        <v>33</v>
+      </c>
+      <c r="N3" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P3" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q3">
         <v>3</v>
       </c>
-      <c r="O3">
+      <c r="R3">
         <v>88</v>
-      </c>
-      <c r="P3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>45</v>
-      </c>
-      <c r="R3" t="s">
-        <v>46</v>
       </c>
       <c r="S3" t="s">
         <v>47</v>
       </c>
-      <c r="T3" s="2">
-        <v>46251.182493078704</v>
-      </c>
-      <c r="U3" s="2">
-        <v>46251.182493078704</v>
+      <c r="T3" t="s">
+        <v>48</v>
+      </c>
+      <c r="U3" t="s">
+        <v>49</v>
       </c>
       <c r="V3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="W3" s="2">
+        <v>46251.1975738426</v>
+      </c>
+      <c r="X3" s="2">
+        <v>46251.1975738426</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B4" s="1">
         <v>46241.29166666667</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E4">
         <v>130</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K4" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="L4" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="M4" t="s">
-        <v>55</v>
-      </c>
-      <c r="N4">
+        <v>33</v>
+      </c>
+      <c r="N4" t="s">
+        <v>56</v>
+      </c>
+      <c r="O4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P4" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q4">
         <v>4</v>
       </c>
-      <c r="O4">
+      <c r="R4">
         <v>74</v>
       </c>
-      <c r="P4" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>57</v>
-      </c>
-      <c r="R4" t="s">
-        <v>58</v>
-      </c>
       <c r="S4" t="s">
-        <v>47</v>
-      </c>
-      <c r="T4" s="2">
-        <v>46251.18249310185</v>
-      </c>
-      <c r="U4" s="2">
-        <v>46251.18249310185</v>
+        <v>59</v>
+      </c>
+      <c r="T4" t="s">
+        <v>60</v>
+      </c>
+      <c r="U4" t="s">
+        <v>61</v>
       </c>
       <c r="V4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+      <c r="W4" s="2">
+        <v>46251.19757386574</v>
+      </c>
+      <c r="X4" s="2">
+        <v>46251.19757386574</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B5" s="1">
         <v>46238.29166666667</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E5">
         <v>55</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>62</v>
-      </c>
-      <c r="H5" t="s">
-        <v>63</v>
-      </c>
-      <c r="I5" t="s">
-        <v>28</v>
+        <v>65</v>
+      </c>
+      <c r="H5">
+        <v>39.4721</v>
+      </c>
+      <c r="I5">
+        <v>-84.2153</v>
       </c>
       <c r="J5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K5" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="L5" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="M5" t="s">
-        <v>65</v>
-      </c>
-      <c r="N5">
+        <v>33</v>
+      </c>
+      <c r="N5" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" t="s">
+        <v>67</v>
+      </c>
+      <c r="P5" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q5">
         <v>5</v>
       </c>
-      <c r="O5">
+      <c r="R5">
         <v>66</v>
       </c>
-      <c r="P5" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>34</v>
-      </c>
-      <c r="R5" t="s">
-        <v>34</v>
-      </c>
       <c r="S5" t="s">
-        <v>36</v>
-      </c>
-      <c r="T5" s="2">
-        <v>46251.182493113425</v>
-      </c>
-      <c r="U5" s="2">
-        <v>46251.182493113425</v>
+        <v>69</v>
+      </c>
+      <c r="T5" t="s">
+        <v>30</v>
+      </c>
+      <c r="U5" t="s">
+        <v>30</v>
       </c>
       <c r="V5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="W5" s="2">
+        <v>46251.19757388889</v>
+      </c>
+      <c r="X5" s="2">
+        <v>46251.19757388889</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B6" s="1">
         <v>46234.29166666667</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E6">
         <v>90</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N6" t="s">
+        <v>34</v>
+      </c>
+      <c r="O6" t="s">
+        <v>74</v>
+      </c>
+      <c r="P6" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q6">
+        <v>4</v>
+      </c>
+      <c r="R6">
         <v>71</v>
       </c>
-      <c r="M6" t="s">
-        <v>72</v>
-      </c>
-      <c r="N6">
-        <v>4</v>
-      </c>
-      <c r="O6">
-        <v>71</v>
-      </c>
-      <c r="P6" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>34</v>
-      </c>
-      <c r="R6" t="s">
-        <v>73</v>
-      </c>
       <c r="S6" t="s">
-        <v>36</v>
-      </c>
-      <c r="T6" s="2">
-        <v>46251.18249313657</v>
-      </c>
-      <c r="U6" s="2">
-        <v>46251.18249313657</v>
+        <v>30</v>
+      </c>
+      <c r="T6" t="s">
+        <v>30</v>
+      </c>
+      <c r="U6" t="s">
+        <v>76</v>
       </c>
       <c r="V6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="W6" s="2">
+        <v>46251.19757390046</v>
+      </c>
+      <c r="X6" s="2">
+        <v>46251.19757390046</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B7" s="1">
         <v>46230.29166666667</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E7">
         <v>60</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H7" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="I7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K7" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="L7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N7" t="s">
+        <v>81</v>
+      </c>
+      <c r="O7" t="s">
+        <v>82</v>
+      </c>
+      <c r="P7" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q7">
+        <v>3</v>
+      </c>
+      <c r="R7">
         <v>79</v>
       </c>
-      <c r="M7" t="s">
-        <v>80</v>
-      </c>
-      <c r="N7">
-        <v>3</v>
-      </c>
-      <c r="O7">
-        <v>79</v>
-      </c>
-      <c r="P7" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>82</v>
-      </c>
-      <c r="R7" t="s">
-        <v>34</v>
-      </c>
       <c r="S7" t="s">
-        <v>36</v>
-      </c>
-      <c r="T7" s="2">
-        <v>46251.18249314815</v>
-      </c>
-      <c r="U7" s="2">
-        <v>46251.18249314815</v>
+        <v>84</v>
+      </c>
+      <c r="T7" t="s">
+        <v>85</v>
+      </c>
+      <c r="U7" t="s">
+        <v>30</v>
       </c>
       <c r="V7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="W7" s="2">
+        <v>46251.19757392361</v>
+      </c>
+      <c r="X7" s="2">
+        <v>46251.19757392361</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B8" s="1">
         <v>46223.29166666667</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E8">
         <v>105</v>
       </c>
       <c r="F8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L8" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="M8" t="s">
-        <v>87</v>
-      </c>
-      <c r="N8">
+        <v>33</v>
+      </c>
+      <c r="N8" t="s">
+        <v>34</v>
+      </c>
+      <c r="O8" t="s">
+        <v>89</v>
+      </c>
+      <c r="P8" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q8">
         <v>4</v>
       </c>
-      <c r="O8">
+      <c r="R8">
         <v>68</v>
       </c>
-      <c r="P8" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>34</v>
-      </c>
-      <c r="R8" t="s">
-        <v>34</v>
-      </c>
       <c r="S8" t="s">
-        <v>36</v>
-      </c>
-      <c r="T8" s="2">
-        <v>46251.18249315972</v>
-      </c>
-      <c r="U8" s="2">
-        <v>46251.18249315972</v>
+        <v>30</v>
+      </c>
+      <c r="T8" t="s">
+        <v>30</v>
+      </c>
+      <c r="U8" t="s">
+        <v>30</v>
       </c>
       <c r="V8" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="W8" s="2">
+        <v>46251.197573935184</v>
+      </c>
+      <c r="X8" s="2">
+        <v>46251.197573935184</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B9" s="1">
         <v>46216.29166666667</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E9">
         <v>45</v>
       </c>
       <c r="F9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L9" t="s">
-        <v>91</v>
+        <v>32</v>
       </c>
       <c r="M9" t="s">
-        <v>92</v>
-      </c>
-      <c r="N9">
+        <v>33</v>
+      </c>
+      <c r="N9" t="s">
+        <v>32</v>
+      </c>
+      <c r="O9" t="s">
+        <v>94</v>
+      </c>
+      <c r="P9" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q9">
         <v>5</v>
       </c>
-      <c r="O9">
+      <c r="R9">
         <v>70</v>
       </c>
-      <c r="P9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>34</v>
-      </c>
-      <c r="R9" t="s">
-        <v>34</v>
-      </c>
       <c r="S9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T9" s="2">
-        <v>46251.18249317129</v>
-      </c>
-      <c r="U9" s="2">
-        <v>46251.18249317129</v>
+        <v>30</v>
+      </c>
+      <c r="T9" t="s">
+        <v>30</v>
+      </c>
+      <c r="U9" t="s">
+        <v>30</v>
       </c>
       <c r="V9" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="W9" s="2">
+        <v>46251.19757394676</v>
+      </c>
+      <c r="X9" s="2">
+        <v>46251.19757394676</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V1"/>
+  <autoFilter ref="A1:Y1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2146,138 +2238,138 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="Y1" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="Z1" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="AA1" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="AB1" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="AC1" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AD1" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="AE1" s="4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AF1" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C2" s="1">
         <v>46248.29166666667</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F2" t="s">
-        <v>34</v>
+        <v>129</v>
       </c>
       <c r="G2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="I2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -2286,96 +2378,96 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>120</v>
+        <v>540</v>
       </c>
       <c r="P2">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="Q2" t="s">
-        <v>127</v>
-      </c>
-      <c r="R2" t="s">
-        <v>34</v>
+        <v>131</v>
+      </c>
+      <c r="R2">
+        <v>4</v>
       </c>
       <c r="S2">
+        <v>4</v>
+      </c>
+      <c r="T2">
         <v>5</v>
       </c>
-      <c r="T2" t="s">
-        <v>34</v>
-      </c>
-      <c r="U2" t="s">
-        <v>34</v>
+      <c r="U2">
+        <v>4</v>
       </c>
       <c r="V2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="W2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="Y2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Z2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="AA2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AC2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AD2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AE2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="C3" s="1">
-        <v>46248.29166666667</v>
+        <v>46230.29166666667</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F3" t="s">
-        <v>135</v>
+        <v>30</v>
       </c>
       <c r="G3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H3" t="s">
         <v>131</v>
       </c>
       <c r="I3" t="s">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="J3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -2384,96 +2476,96 @@
         <v>0</v>
       </c>
       <c r="O3">
-        <v>240</v>
-      </c>
-      <c r="P3" t="s">
-        <v>34</v>
+        <v>720</v>
+      </c>
+      <c r="P3">
+        <v>180</v>
       </c>
       <c r="Q3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R3">
+        <v>3</v>
+      </c>
+      <c r="S3">
         <v>4</v>
       </c>
-      <c r="S3" t="s">
-        <v>34</v>
-      </c>
-      <c r="T3" t="s">
-        <v>34</v>
-      </c>
-      <c r="U3">
+      <c r="T3">
+        <v>3</v>
+      </c>
+      <c r="U3" t="s">
+        <v>30</v>
+      </c>
+      <c r="V3" t="s">
+        <v>30</v>
+      </c>
+      <c r="W3">
         <v>4</v>
       </c>
-      <c r="V3" t="s">
-        <v>34</v>
-      </c>
-      <c r="W3" t="s">
-        <v>34</v>
-      </c>
       <c r="X3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="Y3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Z3" t="s">
-        <v>130</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>34</v>
+        <v>134</v>
+      </c>
+      <c r="AA3">
+        <v>2</v>
       </c>
       <c r="AB3" t="s">
-        <v>34</v>
+        <v>135</v>
       </c>
       <c r="AC3" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="AD3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1">
-        <v>46234.29166666667</v>
+        <v>46248.29166666667</v>
       </c>
       <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>139</v>
+      </c>
+      <c r="H4" t="s">
+        <v>131</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" t="s">
+        <v>145</v>
+      </c>
+      <c r="K4">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
-        <v>141</v>
-      </c>
-      <c r="F4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" t="s">
-        <v>136</v>
-      </c>
-      <c r="H4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J4" t="s">
-        <v>142</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
       <c r="L4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -2482,96 +2574,96 @@
         <v>0</v>
       </c>
       <c r="O4">
-        <v>600</v>
+        <v>120</v>
       </c>
       <c r="P4">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="Q4" t="s">
-        <v>127</v>
-      </c>
-      <c r="R4">
-        <v>4</v>
+        <v>131</v>
+      </c>
+      <c r="R4" t="s">
+        <v>30</v>
       </c>
       <c r="S4">
-        <v>4</v>
-      </c>
-      <c r="T4">
-        <v>4</v>
-      </c>
-      <c r="U4">
         <v>5</v>
       </c>
+      <c r="T4" t="s">
+        <v>30</v>
+      </c>
+      <c r="U4" t="s">
+        <v>30</v>
+      </c>
       <c r="V4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="W4">
         <v>4</v>
       </c>
       <c r="X4" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="Y4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Z4" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="AA4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AC4" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AD4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AE4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF4" t="s">
-        <v>143</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="C5" s="1">
-        <v>46238.29166666667</v>
+        <v>46216.29166666667</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G5" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H5" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="I5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -2580,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="O5">
-        <v>900</v>
+        <v>480</v>
       </c>
       <c r="P5">
-        <v>260</v>
+        <v>30</v>
       </c>
       <c r="Q5" t="s">
-        <v>127</v>
-      </c>
-      <c r="R5">
-        <v>4</v>
+        <v>131</v>
+      </c>
+      <c r="R5" t="s">
+        <v>30</v>
       </c>
       <c r="S5">
         <v>5</v>
@@ -2598,40 +2690,40 @@
         <v>5</v>
       </c>
       <c r="U5" t="s">
-        <v>34</v>
-      </c>
-      <c r="V5">
+        <v>30</v>
+      </c>
+      <c r="V5" t="s">
+        <v>30</v>
+      </c>
+      <c r="W5">
         <v>5</v>
       </c>
-      <c r="W5">
+      <c r="X5" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA5">
         <v>4</v>
       </c>
-      <c r="X5" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>34</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>130</v>
-      </c>
-      <c r="AA5">
-        <v>2</v>
-      </c>
       <c r="AB5" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AC5" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AD5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AE5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF5" t="s">
-        <v>147</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -2639,37 +2731,37 @@
         <v>148</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1">
-        <v>46230.29166666667</v>
+        <v>46248.29166666667</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="s">
         <v>149</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>129</v>
       </c>
       <c r="G6" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H6" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="I6" t="s">
-        <v>34</v>
+        <v>150</v>
       </c>
       <c r="J6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -2678,55 +2770,55 @@
         <v>0</v>
       </c>
       <c r="O6">
-        <v>720</v>
-      </c>
-      <c r="P6">
-        <v>180</v>
+        <v>240</v>
+      </c>
+      <c r="P6" t="s">
+        <v>30</v>
       </c>
       <c r="Q6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R6">
-        <v>3</v>
-      </c>
-      <c r="S6">
         <v>4</v>
       </c>
-      <c r="T6">
-        <v>3</v>
-      </c>
-      <c r="U6" t="s">
-        <v>34</v>
+      <c r="S6" t="s">
+        <v>30</v>
+      </c>
+      <c r="T6" t="s">
+        <v>30</v>
+      </c>
+      <c r="U6">
+        <v>4</v>
       </c>
       <c r="V6" t="s">
-        <v>34</v>
-      </c>
-      <c r="W6">
-        <v>4</v>
+        <v>30</v>
+      </c>
+      <c r="W6" t="s">
+        <v>30</v>
       </c>
       <c r="X6" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="Y6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Z6" t="s">
-        <v>130</v>
-      </c>
-      <c r="AA6">
-        <v>2</v>
+        <v>134</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>30</v>
       </c>
       <c r="AB6" t="s">
-        <v>131</v>
+        <v>30</v>
       </c>
       <c r="AC6" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="AD6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AE6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF6" t="s">
         <v>152</v>
@@ -2737,192 +2829,192 @@
         <v>153</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C7" s="1">
-        <v>46216.29166666667</v>
+        <v>46223.29166666667</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>155</v>
       </c>
       <c r="G7" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="I7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J7" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M7">
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7">
-        <v>480</v>
+        <v>1800</v>
       </c>
       <c r="P7">
-        <v>30</v>
+        <v>320</v>
       </c>
       <c r="Q7" t="s">
-        <v>127</v>
-      </c>
-      <c r="R7" t="s">
-        <v>34</v>
+        <v>131</v>
+      </c>
+      <c r="R7">
+        <v>4</v>
       </c>
       <c r="S7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T7">
-        <v>5</v>
-      </c>
-      <c r="U7" t="s">
-        <v>34</v>
-      </c>
-      <c r="V7" t="s">
-        <v>34</v>
+        <v>4</v>
+      </c>
+      <c r="U7">
+        <v>4</v>
+      </c>
+      <c r="V7">
+        <v>4</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X7" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="Y7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Z7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="AA7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB7" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AC7" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AD7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AE7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C8" s="1">
-        <v>46241.29166666667</v>
+        <v>46245.29166666667</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F8" t="s">
-        <v>157</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="H8" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="I8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J8" t="s">
         <v>159</v>
       </c>
       <c r="K8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M8">
         <v>1</v>
       </c>
       <c r="N8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>1500</v>
+        <v>780</v>
       </c>
       <c r="P8">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="Q8" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S8">
         <v>4</v>
       </c>
       <c r="T8">
-        <v>5</v>
-      </c>
-      <c r="U8">
+        <v>3</v>
+      </c>
+      <c r="U8" t="s">
+        <v>30</v>
+      </c>
+      <c r="V8">
+        <v>3</v>
+      </c>
+      <c r="W8">
         <v>4</v>
       </c>
-      <c r="V8">
-        <v>4</v>
-      </c>
-      <c r="W8">
-        <v>5</v>
-      </c>
       <c r="X8" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="Y8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Z8" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="AA8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AC8" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="AD8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AE8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF8" t="s">
         <v>160</v>
@@ -2933,10 +3025,10 @@
         <v>161</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="C9" s="1">
-        <v>46245.29166666667</v>
+        <v>46238.29166666667</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -2945,82 +3037,82 @@
         <v>162</v>
       </c>
       <c r="F9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="I9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J9" t="s">
         <v>163</v>
       </c>
       <c r="K9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L9">
         <v>2</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9">
         <v>0</v>
       </c>
       <c r="O9">
-        <v>780</v>
+        <v>900</v>
       </c>
       <c r="P9">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="Q9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="V9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W9">
         <v>4</v>
       </c>
       <c r="X9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="Y9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Z9" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="AA9">
         <v>2</v>
       </c>
       <c r="AB9" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AC9" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="AD9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AE9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF9" t="s">
         <v>164</v>
@@ -3031,37 +3123,37 @@
         <v>165</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="C10" s="1">
-        <v>46248.29166666667</v>
+        <v>46234.29166666667</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="F10" t="s">
-        <v>135</v>
+        <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H10" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="I10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -3070,13 +3162,13 @@
         <v>0</v>
       </c>
       <c r="O10">
-        <v>540</v>
+        <v>600</v>
       </c>
       <c r="P10">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="Q10" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R10">
         <v>4</v>
@@ -3085,105 +3177,105 @@
         <v>4</v>
       </c>
       <c r="T10">
+        <v>4</v>
+      </c>
+      <c r="U10">
         <v>5</v>
       </c>
-      <c r="U10">
+      <c r="V10" t="s">
+        <v>30</v>
+      </c>
+      <c r="W10">
         <v>4</v>
       </c>
-      <c r="V10" t="s">
-        <v>34</v>
-      </c>
-      <c r="W10">
-        <v>5</v>
-      </c>
       <c r="X10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="Y10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Z10" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="AA10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB10" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AC10" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AD10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AE10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF10" t="s">
-        <v>34</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="C11" s="1">
-        <v>46223.29166666667</v>
+        <v>46241.29166666667</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="F11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G11" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="H11" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="I11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K11">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11">
         <v>1</v>
       </c>
       <c r="O11">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="P11">
-        <v>320</v>
+        <v>210</v>
       </c>
       <c r="Q11" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S11">
         <v>4</v>
       </c>
       <c r="T11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U11">
         <v>4</v>
@@ -3192,34 +3284,34 @@
         <v>4</v>
       </c>
       <c r="W11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X11" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="Y11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Z11" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="AA11">
         <v>3</v>
       </c>
       <c r="AB11" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AC11" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AD11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AE11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF11" t="s">
-        <v>34</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -3253,1772 +3345,1772 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="D2" s="1">
-        <v>46248.29166666667</v>
+        <v>46230.29166666667</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="I2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="J2" t="s">
-        <v>34</v>
+        <v>194</v>
       </c>
       <c r="K2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="L2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" t="s">
-        <v>34</v>
+        <v>30</v>
+      </c>
+      <c r="M2">
+        <v>4</v>
       </c>
       <c r="N2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="O2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P2" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="Q2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="R2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="S2" t="s">
-        <v>34</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B3" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="D3" s="1">
-        <v>46241.29166666667</v>
+        <v>46216.29166666667</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="I3" t="s">
+        <v>200</v>
+      </c>
+      <c r="J3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" t="s">
         <v>195</v>
       </c>
-      <c r="J3" t="s">
-        <v>196</v>
-      </c>
-      <c r="K3" t="s">
-        <v>191</v>
-      </c>
       <c r="L3" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3">
-        <v>4</v>
+        <v>30</v>
+      </c>
+      <c r="M3" t="s">
+        <v>30</v>
       </c>
       <c r="N3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="O3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P3" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="Q3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="S3" t="s">
-        <v>198</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B4" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="D4" s="1">
-        <v>46230.29166666667</v>
+        <v>46241.29166666667</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="I4" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="J4" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="K4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="L4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M4">
         <v>4</v>
       </c>
       <c r="N4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="O4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P4" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="Q4" t="s">
         <v>131</v>
       </c>
       <c r="R4" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="S4" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B5" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="D5" s="1">
-        <v>46223.29166666667</v>
+        <v>46245.29166666667</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" t="s">
+        <v>209</v>
+      </c>
+      <c r="I5" t="s">
+        <v>210</v>
+      </c>
+      <c r="J5" t="s">
+        <v>211</v>
+      </c>
+      <c r="K5" t="s">
+        <v>195</v>
+      </c>
+      <c r="L5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5">
+        <v>4</v>
+      </c>
+      <c r="N5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P5" t="s">
         <v>34</v>
       </c>
-      <c r="H5" t="s">
-        <v>205</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="Q5" t="s">
+        <v>131</v>
+      </c>
+      <c r="R5" t="s">
         <v>206</v>
       </c>
-      <c r="J5" t="s">
-        <v>207</v>
-      </c>
-      <c r="K5" t="s">
-        <v>191</v>
-      </c>
-      <c r="L5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5">
-        <v>5</v>
-      </c>
-      <c r="N5" t="s">
-        <v>34</v>
-      </c>
-      <c r="O5" t="s">
-        <v>34</v>
-      </c>
-      <c r="P5" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>127</v>
-      </c>
-      <c r="R5" t="s">
-        <v>192</v>
-      </c>
       <c r="S5" t="s">
-        <v>34</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="D6" s="1">
-        <v>46238.29166666667</v>
+        <v>46216.29166666667</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F6" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H6" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="I6" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="J6" t="s">
-        <v>201</v>
+        <v>30</v>
       </c>
       <c r="K6" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="L6" t="s">
-        <v>34</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
+        <v>30</v>
+      </c>
+      <c r="M6" t="s">
+        <v>30</v>
       </c>
       <c r="N6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="O6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Q6" t="s">
         <v>131</v>
       </c>
       <c r="R6" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="S6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B7" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="D7" s="1">
-        <v>46245.29166666667</v>
+        <v>46216.29166666667</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H7" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I7" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="J7" t="s">
-        <v>214</v>
+        <v>30</v>
       </c>
       <c r="K7" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="L7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M7">
-        <v>4</v>
+        <v>30</v>
+      </c>
+      <c r="M7" t="s">
+        <v>30</v>
       </c>
       <c r="N7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="O7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R7" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="S7" t="s">
-        <v>215</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B8" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D8" s="1">
         <v>46241.29166666667</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I8" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J8" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="K8" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L8" t="s">
-        <v>34</v>
-      </c>
-      <c r="M8" t="s">
-        <v>34</v>
+        <v>30</v>
+      </c>
+      <c r="M8">
+        <v>3</v>
       </c>
       <c r="N8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="O8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q8" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R8" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="S8" t="s">
-        <v>34</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="D9" s="1">
-        <v>46241.29166666667</v>
+        <v>46223.29166666667</v>
       </c>
       <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>191</v>
+      </c>
+      <c r="G9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" t="s">
+        <v>225</v>
+      </c>
+      <c r="I9" t="s">
+        <v>226</v>
+      </c>
+      <c r="J9" t="s">
+        <v>221</v>
+      </c>
+      <c r="K9" t="s">
+        <v>222</v>
+      </c>
+      <c r="L9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M9">
         <v>4</v>
       </c>
-      <c r="F9" t="s">
-        <v>188</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="N9" t="s">
+        <v>30</v>
+      </c>
+      <c r="O9" t="s">
+        <v>30</v>
+      </c>
+      <c r="P9" t="s">
         <v>34</v>
       </c>
-      <c r="H9" t="s">
-        <v>221</v>
-      </c>
-      <c r="I9" t="s">
-        <v>222</v>
-      </c>
-      <c r="J9" t="s">
-        <v>223</v>
-      </c>
-      <c r="K9" t="s">
-        <v>219</v>
-      </c>
-      <c r="L9" t="s">
-        <v>34</v>
-      </c>
-      <c r="M9">
-        <v>3</v>
-      </c>
-      <c r="N9" t="s">
-        <v>34</v>
-      </c>
-      <c r="O9" t="s">
-        <v>34</v>
-      </c>
-      <c r="P9" t="s">
-        <v>53</v>
-      </c>
       <c r="Q9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R9" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="S9" t="s">
-        <v>224</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="D10" s="1">
-        <v>46223.29166666667</v>
+        <v>46234.29166666667</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F10" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" t="s">
+        <v>228</v>
+      </c>
+      <c r="I10" t="s">
+        <v>229</v>
+      </c>
+      <c r="J10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" t="s">
+        <v>195</v>
+      </c>
+      <c r="L10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P10" t="s">
         <v>34</v>
       </c>
-      <c r="H10" t="s">
-        <v>226</v>
-      </c>
-      <c r="I10" t="s">
-        <v>227</v>
-      </c>
-      <c r="J10" t="s">
-        <v>223</v>
-      </c>
-      <c r="K10" t="s">
-        <v>219</v>
-      </c>
-      <c r="L10" t="s">
-        <v>34</v>
-      </c>
-      <c r="M10">
-        <v>4</v>
-      </c>
-      <c r="N10" t="s">
-        <v>34</v>
-      </c>
-      <c r="O10" t="s">
-        <v>34</v>
-      </c>
-      <c r="P10" t="s">
-        <v>30</v>
-      </c>
       <c r="Q10" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R10" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="S10" t="s">
-        <v>34</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>232</v>
+      </c>
+      <c r="B11" t="s">
+        <v>165</v>
+      </c>
+      <c r="C11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="1">
+        <v>46234.29166666667</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>191</v>
+      </c>
+      <c r="G11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" t="s">
         <v>228</v>
       </c>
-      <c r="B11" t="s">
-        <v>153</v>
-      </c>
-      <c r="C11" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11" s="1">
-        <v>46216.29166666667</v>
-      </c>
-      <c r="E11">
-        <v>3</v>
-      </c>
-      <c r="F11" t="s">
-        <v>188</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="I11" t="s">
+        <v>233</v>
+      </c>
+      <c r="J11" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11" t="s">
+        <v>195</v>
+      </c>
+      <c r="L11" t="s">
+        <v>30</v>
+      </c>
+      <c r="M11" t="s">
+        <v>30</v>
+      </c>
+      <c r="N11" t="s">
+        <v>30</v>
+      </c>
+      <c r="O11" t="s">
+        <v>30</v>
+      </c>
+      <c r="P11" t="s">
         <v>34</v>
       </c>
-      <c r="H11" t="s">
-        <v>205</v>
-      </c>
-      <c r="I11" t="s">
-        <v>229</v>
-      </c>
-      <c r="J11" t="s">
-        <v>34</v>
-      </c>
-      <c r="K11" t="s">
-        <v>191</v>
-      </c>
-      <c r="L11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M11" t="s">
-        <v>34</v>
-      </c>
-      <c r="N11" t="s">
-        <v>34</v>
-      </c>
-      <c r="O11" t="s">
-        <v>34</v>
-      </c>
-      <c r="P11" t="s">
-        <v>28</v>
-      </c>
       <c r="Q11" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R11" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="S11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B12" t="s">
         <v>153</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D12" s="1">
-        <v>46216.29166666667</v>
+        <v>46223.29166666667</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" t="s">
+        <v>216</v>
+      </c>
+      <c r="I12" t="s">
+        <v>235</v>
+      </c>
+      <c r="J12" t="s">
+        <v>236</v>
+      </c>
+      <c r="K12" t="s">
+        <v>195</v>
+      </c>
+      <c r="L12" t="s">
+        <v>30</v>
+      </c>
+      <c r="M12">
+        <v>5</v>
+      </c>
+      <c r="N12" t="s">
+        <v>30</v>
+      </c>
+      <c r="O12" t="s">
+        <v>30</v>
+      </c>
+      <c r="P12" t="s">
         <v>34</v>
       </c>
-      <c r="H12" t="s">
-        <v>217</v>
-      </c>
-      <c r="I12" t="s">
-        <v>231</v>
-      </c>
-      <c r="J12" t="s">
-        <v>34</v>
-      </c>
-      <c r="K12" t="s">
-        <v>191</v>
-      </c>
-      <c r="L12" t="s">
-        <v>34</v>
-      </c>
-      <c r="M12" t="s">
-        <v>34</v>
-      </c>
-      <c r="N12" t="s">
-        <v>34</v>
-      </c>
-      <c r="O12" t="s">
-        <v>34</v>
-      </c>
-      <c r="P12" t="s">
-        <v>28</v>
-      </c>
       <c r="Q12" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R12" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="S12" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B13" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="D13" s="1">
-        <v>46234.29166666667</v>
+        <v>46248.29166666667</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" t="s">
+        <v>228</v>
+      </c>
+      <c r="I13" t="s">
+        <v>238</v>
+      </c>
+      <c r="J13" t="s">
+        <v>236</v>
+      </c>
+      <c r="K13" t="s">
+        <v>195</v>
+      </c>
+      <c r="L13" t="s">
+        <v>30</v>
+      </c>
+      <c r="M13" t="s">
+        <v>30</v>
+      </c>
+      <c r="N13" t="s">
+        <v>30</v>
+      </c>
+      <c r="O13" t="s">
+        <v>30</v>
+      </c>
+      <c r="P13" t="s">
         <v>34</v>
       </c>
-      <c r="H13" t="s">
-        <v>221</v>
-      </c>
-      <c r="I13" t="s">
-        <v>233</v>
-      </c>
-      <c r="J13" t="s">
-        <v>34</v>
-      </c>
-      <c r="K13" t="s">
-        <v>191</v>
-      </c>
-      <c r="L13" t="s">
-        <v>34</v>
-      </c>
-      <c r="M13" t="s">
-        <v>34</v>
-      </c>
-      <c r="N13" t="s">
-        <v>34</v>
-      </c>
-      <c r="O13" t="s">
-        <v>34</v>
-      </c>
-      <c r="P13" t="s">
-        <v>30</v>
-      </c>
       <c r="Q13" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R13" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="S13" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B14" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D14" s="1">
         <v>46241.29166666667</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G14" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H14" t="s">
-        <v>189</v>
+        <v>228</v>
       </c>
       <c r="I14" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="J14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="K14" t="s">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="L14" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M14" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="N14" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="O14" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P14" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="Q14" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R14" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="S14" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B15" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D15" s="1">
-        <v>46223.29166666667</v>
+        <v>46216.29166666667</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G15" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H15" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I15" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="J15" t="s">
+        <v>30</v>
+      </c>
+      <c r="K15" t="s">
+        <v>195</v>
+      </c>
+      <c r="L15" t="s">
+        <v>30</v>
+      </c>
+      <c r="M15" t="s">
+        <v>30</v>
+      </c>
+      <c r="N15" t="s">
+        <v>30</v>
+      </c>
+      <c r="O15" t="s">
+        <v>30</v>
+      </c>
+      <c r="P15" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>131</v>
+      </c>
+      <c r="R15" t="s">
         <v>201</v>
       </c>
-      <c r="K15" t="s">
-        <v>191</v>
-      </c>
-      <c r="L15" t="s">
-        <v>34</v>
-      </c>
-      <c r="M15">
-        <v>3</v>
-      </c>
-      <c r="N15" t="s">
-        <v>34</v>
-      </c>
-      <c r="O15" t="s">
-        <v>34</v>
-      </c>
-      <c r="P15" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>127</v>
-      </c>
-      <c r="R15" t="s">
-        <v>192</v>
-      </c>
       <c r="S15" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B16" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="D16" s="1">
-        <v>46216.29166666667</v>
+        <v>46241.29166666667</v>
       </c>
       <c r="E16">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G16" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H16" t="s">
-        <v>221</v>
+        <v>192</v>
       </c>
       <c r="I16" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="J16" t="s">
-        <v>34</v>
+        <v>236</v>
       </c>
       <c r="K16" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="L16" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M16" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="N16" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="O16" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P16" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="Q16" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="S16" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B17" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="D17" s="1">
-        <v>46241.29166666667</v>
+        <v>46234.29166666667</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G17" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H17" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I17" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="J17" t="s">
-        <v>196</v>
+        <v>30</v>
       </c>
       <c r="K17" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="L17" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M17">
         <v>4</v>
       </c>
       <c r="N17" t="s">
+        <v>30</v>
+      </c>
+      <c r="O17" t="s">
+        <v>30</v>
+      </c>
+      <c r="P17" t="s">
         <v>34</v>
       </c>
-      <c r="O17" t="s">
-        <v>34</v>
-      </c>
-      <c r="P17" t="s">
-        <v>53</v>
-      </c>
       <c r="Q17" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R17" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="S17" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B18" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="D18" s="1">
-        <v>46216.29166666667</v>
+        <v>46234.29166666667</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G18" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18" t="s">
+        <v>219</v>
+      </c>
+      <c r="I18" t="s">
+        <v>248</v>
+      </c>
+      <c r="J18" t="s">
+        <v>30</v>
+      </c>
+      <c r="K18" t="s">
+        <v>195</v>
+      </c>
+      <c r="L18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M18" t="s">
+        <v>30</v>
+      </c>
+      <c r="N18" t="s">
+        <v>30</v>
+      </c>
+      <c r="O18" t="s">
+        <v>30</v>
+      </c>
+      <c r="P18" t="s">
         <v>34</v>
       </c>
-      <c r="H18" t="s">
-        <v>212</v>
-      </c>
-      <c r="I18" t="s">
-        <v>243</v>
-      </c>
-      <c r="J18" t="s">
-        <v>34</v>
-      </c>
-      <c r="K18" t="s">
-        <v>191</v>
-      </c>
-      <c r="L18" t="s">
-        <v>34</v>
-      </c>
-      <c r="M18" t="s">
-        <v>34</v>
-      </c>
-      <c r="N18" t="s">
-        <v>34</v>
-      </c>
-      <c r="O18" t="s">
-        <v>34</v>
-      </c>
-      <c r="P18" t="s">
-        <v>28</v>
-      </c>
       <c r="Q18" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R18" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="S18" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B19" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D19" s="1">
-        <v>46248.29166666667</v>
+        <v>46245.29166666667</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G19" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" t="s">
+        <v>228</v>
+      </c>
+      <c r="I19" t="s">
+        <v>250</v>
+      </c>
+      <c r="J19" t="s">
+        <v>30</v>
+      </c>
+      <c r="K19" t="s">
+        <v>222</v>
+      </c>
+      <c r="L19" t="s">
+        <v>30</v>
+      </c>
+      <c r="M19" t="s">
+        <v>30</v>
+      </c>
+      <c r="N19" t="s">
+        <v>30</v>
+      </c>
+      <c r="O19" t="s">
+        <v>30</v>
+      </c>
+      <c r="P19" t="s">
         <v>34</v>
       </c>
-      <c r="H19" t="s">
-        <v>205</v>
-      </c>
-      <c r="I19" t="s">
-        <v>245</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="Q19" t="s">
+        <v>131</v>
+      </c>
+      <c r="R19" t="s">
         <v>201</v>
       </c>
-      <c r="K19" t="s">
-        <v>191</v>
-      </c>
-      <c r="L19" t="s">
-        <v>34</v>
-      </c>
-      <c r="M19">
-        <v>5</v>
-      </c>
-      <c r="N19" t="s">
-        <v>34</v>
-      </c>
-      <c r="O19" t="s">
-        <v>34</v>
-      </c>
-      <c r="P19" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>127</v>
-      </c>
-      <c r="R19" t="s">
-        <v>192</v>
-      </c>
       <c r="S19" t="s">
-        <v>246</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B20" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C20" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="D20" s="1">
-        <v>46230.29166666667</v>
+        <v>46248.29166666667</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" t="s">
+        <v>192</v>
+      </c>
+      <c r="I20" t="s">
+        <v>252</v>
+      </c>
+      <c r="J20" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20" t="s">
+        <v>195</v>
+      </c>
+      <c r="L20" t="s">
+        <v>30</v>
+      </c>
+      <c r="M20" t="s">
+        <v>30</v>
+      </c>
+      <c r="N20" t="s">
+        <v>30</v>
+      </c>
+      <c r="O20" t="s">
+        <v>30</v>
+      </c>
+      <c r="P20" t="s">
         <v>34</v>
       </c>
-      <c r="H20" t="s">
-        <v>217</v>
-      </c>
-      <c r="I20" t="s">
-        <v>248</v>
-      </c>
-      <c r="J20" t="s">
+      <c r="Q20" t="s">
+        <v>135</v>
+      </c>
+      <c r="R20" t="s">
         <v>201</v>
       </c>
-      <c r="K20" t="s">
-        <v>219</v>
-      </c>
-      <c r="L20" t="s">
-        <v>34</v>
-      </c>
-      <c r="M20" t="s">
-        <v>34</v>
-      </c>
-      <c r="N20" t="s">
-        <v>34</v>
-      </c>
-      <c r="O20" t="s">
-        <v>34</v>
-      </c>
-      <c r="P20" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>131</v>
-      </c>
-      <c r="R20" t="s">
-        <v>192</v>
-      </c>
       <c r="S20" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B21" t="s">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D21" s="1">
-        <v>46238.29166666667</v>
+        <v>46241.29166666667</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F21" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G21" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H21" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="I21" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="J21" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="K21" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="L21" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M21" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="N21" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="O21" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P21" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="Q21" t="s">
         <v>131</v>
       </c>
       <c r="R21" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="S21" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B22" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D22" s="1">
-        <v>46245.29166666667</v>
+        <v>46241.29166666667</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G22" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H22" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I22" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="J22" t="s">
-        <v>34</v>
+        <v>205</v>
       </c>
       <c r="K22" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="L22" t="s">
-        <v>34</v>
-      </c>
-      <c r="M22" t="s">
-        <v>34</v>
+        <v>30</v>
+      </c>
+      <c r="M22">
+        <v>4</v>
       </c>
       <c r="N22" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="O22" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P22" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="Q22" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R22" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="S22" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B23" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="C23" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="D23" s="1">
-        <v>46234.29166666667</v>
+        <v>46223.29166666667</v>
       </c>
       <c r="E23">
         <v>2</v>
       </c>
       <c r="F23" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G23" t="s">
+        <v>30</v>
+      </c>
+      <c r="H23" t="s">
+        <v>228</v>
+      </c>
+      <c r="I23" t="s">
+        <v>258</v>
+      </c>
+      <c r="J23" t="s">
+        <v>194</v>
+      </c>
+      <c r="K23" t="s">
+        <v>195</v>
+      </c>
+      <c r="L23" t="s">
+        <v>30</v>
+      </c>
+      <c r="M23">
+        <v>3</v>
+      </c>
+      <c r="N23" t="s">
+        <v>30</v>
+      </c>
+      <c r="O23" t="s">
+        <v>30</v>
+      </c>
+      <c r="P23" t="s">
         <v>34</v>
       </c>
-      <c r="H23" t="s">
-        <v>254</v>
-      </c>
-      <c r="I23" t="s">
-        <v>255</v>
-      </c>
-      <c r="J23" t="s">
-        <v>34</v>
-      </c>
-      <c r="K23" t="s">
-        <v>191</v>
-      </c>
-      <c r="L23" t="s">
-        <v>34</v>
-      </c>
-      <c r="M23">
-        <v>4</v>
-      </c>
-      <c r="N23" t="s">
-        <v>34</v>
-      </c>
-      <c r="O23" t="s">
-        <v>34</v>
-      </c>
-      <c r="P23" t="s">
-        <v>30</v>
-      </c>
       <c r="Q23" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R23" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="S23" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B24" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D24" s="1">
-        <v>46234.29166666667</v>
+        <v>46230.29166666667</v>
       </c>
       <c r="E24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G24" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H24" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="I24" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="J24" t="s">
-        <v>34</v>
+        <v>194</v>
       </c>
       <c r="K24" t="s">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="L24" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M24" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="N24" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="O24" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P24" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="Q24" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="R24" t="s">
-        <v>258</v>
+        <v>201</v>
       </c>
       <c r="S24" t="s">
-        <v>259</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B25" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="D25" s="1">
-        <v>46216.29166666667</v>
+        <v>46245.29166666667</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G25" t="s">
+        <v>30</v>
+      </c>
+      <c r="H25" t="s">
+        <v>199</v>
+      </c>
+      <c r="I25" t="s">
+        <v>262</v>
+      </c>
+      <c r="J25" t="s">
+        <v>30</v>
+      </c>
+      <c r="K25" t="s">
+        <v>195</v>
+      </c>
+      <c r="L25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M25" t="s">
+        <v>30</v>
+      </c>
+      <c r="N25" t="s">
+        <v>30</v>
+      </c>
+      <c r="O25" t="s">
+        <v>30</v>
+      </c>
+      <c r="P25" t="s">
         <v>34</v>
       </c>
-      <c r="H25" t="s">
-        <v>189</v>
-      </c>
-      <c r="I25" t="s">
-        <v>261</v>
-      </c>
-      <c r="J25" t="s">
-        <v>34</v>
-      </c>
-      <c r="K25" t="s">
-        <v>191</v>
-      </c>
-      <c r="L25" t="s">
-        <v>34</v>
-      </c>
-      <c r="M25" t="s">
-        <v>34</v>
-      </c>
-      <c r="N25" t="s">
-        <v>34</v>
-      </c>
-      <c r="O25" t="s">
-        <v>34</v>
-      </c>
-      <c r="P25" t="s">
-        <v>28</v>
-      </c>
       <c r="Q25" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R25" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="S25" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C26" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="D26" s="1">
-        <v>46234.29166666667</v>
+        <v>46216.29166666667</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G26" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H26" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="I26" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J26" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K26" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="L26" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M26" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="N26" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="O26" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P26" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q26" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R26" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="S26" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B27" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="D27" s="1">
-        <v>46241.29166666667</v>
+        <v>46216.29166666667</v>
       </c>
       <c r="E27">
         <v>5</v>
       </c>
       <c r="F27" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G27" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H27" t="s">
-        <v>254</v>
+        <v>209</v>
       </c>
       <c r="I27" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J27" t="s">
-        <v>214</v>
+        <v>30</v>
       </c>
       <c r="K27" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="L27" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M27" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="N27" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="O27" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P27" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="Q27" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R27" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="S27" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="C28" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D28" s="1">
         <v>46248.29166666667</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G28" t="s">
+        <v>30</v>
+      </c>
+      <c r="H28" t="s">
+        <v>216</v>
+      </c>
+      <c r="I28" t="s">
+        <v>268</v>
+      </c>
+      <c r="J28" t="s">
+        <v>194</v>
+      </c>
+      <c r="K28" t="s">
+        <v>195</v>
+      </c>
+      <c r="L28" t="s">
+        <v>30</v>
+      </c>
+      <c r="M28">
+        <v>5</v>
+      </c>
+      <c r="N28" t="s">
+        <v>30</v>
+      </c>
+      <c r="O28" t="s">
+        <v>30</v>
+      </c>
+      <c r="P28" t="s">
         <v>34</v>
       </c>
-      <c r="H28" t="s">
-        <v>217</v>
-      </c>
-      <c r="I28" t="s">
-        <v>267</v>
-      </c>
-      <c r="J28" t="s">
-        <v>207</v>
-      </c>
-      <c r="K28" t="s">
-        <v>191</v>
-      </c>
-      <c r="L28" t="s">
-        <v>34</v>
-      </c>
-      <c r="M28" t="s">
-        <v>34</v>
-      </c>
-      <c r="N28" t="s">
-        <v>34</v>
-      </c>
-      <c r="O28" t="s">
-        <v>34</v>
-      </c>
-      <c r="P28" t="s">
-        <v>30</v>
-      </c>
       <c r="Q28" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="R28" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="S28" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B29" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="D29" s="1">
-        <v>46216.29166666667</v>
+        <v>46238.29166666667</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G29" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H29" t="s">
-        <v>254</v>
+        <v>192</v>
       </c>
       <c r="I29" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J29" t="s">
-        <v>34</v>
+        <v>194</v>
       </c>
       <c r="K29" t="s">
-        <v>191</v>
+        <v>272</v>
       </c>
       <c r="L29" t="s">
-        <v>34</v>
-      </c>
-      <c r="M29" t="s">
-        <v>34</v>
+        <v>30</v>
+      </c>
+      <c r="M29">
+        <v>5</v>
       </c>
       <c r="N29" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="O29" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P29" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Q29" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="R29" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="S29" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B30" t="s">
         <v>161</v>
       </c>
       <c r="C30" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D30" s="1">
-        <v>46245.29166666667</v>
+        <v>46238.29166666667</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F30" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G30" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H30" t="s">
-        <v>254</v>
+        <v>228</v>
       </c>
       <c r="I30" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="J30" t="s">
-        <v>34</v>
+        <v>211</v>
       </c>
       <c r="K30" t="s">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="L30" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M30" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="N30" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="O30" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P30" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q30" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="R30" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="S30" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -5047,857 +5139,857 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C2" s="1">
         <v>46248.29166666667</v>
       </c>
       <c r="D2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F2" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G2" t="s">
-        <v>190</v>
+        <v>238</v>
       </c>
       <c r="H2" t="s">
-        <v>187</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C3" s="1">
         <v>46248.29166666667</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="E3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F3" t="s">
-        <v>275</v>
+        <v>201</v>
       </c>
       <c r="G3" t="s">
-        <v>138</v>
+        <v>268</v>
       </c>
       <c r="H3" t="s">
-        <v>34</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C4" s="1">
-        <v>46234.29166666667</v>
+        <v>46230.29166666667</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="G4" t="s">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="H4" t="s">
-        <v>232</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C5" s="1">
-        <v>46234.29166666667</v>
+        <v>46230.29166666667</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F5" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G5" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="H5" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C6" s="1">
-        <v>46234.29166666667</v>
+        <v>46248.29166666667</v>
       </c>
       <c r="D6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E6" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F6" t="s">
-        <v>258</v>
+        <v>201</v>
       </c>
       <c r="G6" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="H6" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C7" s="1">
-        <v>46234.29166666667</v>
+        <v>46216.29166666667</v>
       </c>
       <c r="D7" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E7" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F7" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G7" t="s">
-        <v>263</v>
+        <v>200</v>
       </c>
       <c r="H7" t="s">
-        <v>262</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="B8" t="s">
+        <v>146</v>
+      </c>
+      <c r="C8" s="1">
+        <v>46216.29166666667</v>
+      </c>
+      <c r="D8" t="s">
         <v>144</v>
       </c>
-      <c r="C8" s="1">
-        <v>46238.29166666667</v>
-      </c>
-      <c r="D8" t="s">
-        <v>145</v>
-      </c>
       <c r="E8" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F8" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G8" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="H8" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="B9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C9" s="1">
+        <v>46216.29166666667</v>
+      </c>
+      <c r="D9" t="s">
         <v>144</v>
       </c>
-      <c r="C9" s="1">
-        <v>46238.29166666667</v>
-      </c>
-      <c r="D9" t="s">
-        <v>145</v>
-      </c>
       <c r="E9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F9" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G9" t="s">
-        <v>250</v>
+        <v>217</v>
       </c>
       <c r="H9" t="s">
-        <v>249</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="B10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C10" s="1">
-        <v>46230.29166666667</v>
+        <v>46216.29166666667</v>
       </c>
       <c r="D10" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F10" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G10" t="s">
-        <v>200</v>
+        <v>242</v>
       </c>
       <c r="H10" t="s">
-        <v>199</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="B11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C11" s="1">
-        <v>46230.29166666667</v>
+        <v>46216.29166666667</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E11" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F11" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G11" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="H11" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B12" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C12" s="1">
         <v>46216.29166666667</v>
       </c>
       <c r="D12" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="E12" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F12" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G12" t="s">
-        <v>229</v>
+        <v>266</v>
       </c>
       <c r="H12" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C13" s="1">
-        <v>46216.29166666667</v>
+        <v>46248.29166666667</v>
       </c>
       <c r="D13" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="E13" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F13" t="s">
-        <v>192</v>
+        <v>278</v>
       </c>
       <c r="G13" t="s">
-        <v>231</v>
+        <v>151</v>
       </c>
       <c r="H13" t="s">
-        <v>230</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
         <v>153</v>
       </c>
       <c r="C14" s="1">
-        <v>46216.29166666667</v>
+        <v>46223.29166666667</v>
       </c>
       <c r="D14" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="E14" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F14" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G14" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="H14" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s">
         <v>153</v>
       </c>
       <c r="C15" s="1">
-        <v>46216.29166666667</v>
+        <v>46223.29166666667</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="E15" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F15" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G15" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="H15" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B16" t="s">
         <v>153</v>
       </c>
       <c r="C16" s="1">
-        <v>46216.29166666667</v>
+        <v>46223.29166666667</v>
       </c>
       <c r="D16" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="E16" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F16" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G16" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H16" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B17" t="s">
         <v>153</v>
       </c>
       <c r="C17" s="1">
-        <v>46216.29166666667</v>
+        <v>46223.29166666667</v>
       </c>
       <c r="D17" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="E17" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F17" t="s">
-        <v>192</v>
+        <v>279</v>
       </c>
       <c r="G17" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="H17" t="s">
-        <v>268</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C18" s="1">
-        <v>46241.29166666667</v>
+        <v>46245.29166666667</v>
       </c>
       <c r="D18" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E18" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="F18" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="G18" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="H18" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B19" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C19" s="1">
-        <v>46241.29166666667</v>
+        <v>46245.29166666667</v>
       </c>
       <c r="D19" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E19" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="F19" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G19" t="s">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="H19" t="s">
-        <v>216</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C20" s="1">
-        <v>46241.29166666667</v>
+        <v>46245.29166666667</v>
       </c>
       <c r="D20" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E20" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="F20" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G20" t="s">
-        <v>222</v>
+        <v>262</v>
       </c>
       <c r="H20" t="s">
-        <v>220</v>
+        <v>261</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B21" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C21" s="1">
-        <v>46241.29166666667</v>
+        <v>46238.29166666667</v>
       </c>
       <c r="D21" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E21" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="F21" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G21" t="s">
-        <v>235</v>
+        <v>271</v>
       </c>
       <c r="H21" t="s">
-        <v>234</v>
+        <v>270</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B22" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C22" s="1">
-        <v>46241.29166666667</v>
+        <v>46238.29166666667</v>
       </c>
       <c r="D22" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E22" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="F22" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G22" t="s">
-        <v>241</v>
+        <v>274</v>
       </c>
       <c r="H22" t="s">
-        <v>240</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="B23" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="C23" s="1">
-        <v>46241.29166666667</v>
+        <v>46234.29166666667</v>
       </c>
       <c r="D23" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E23" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="F23" t="s">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="G23" t="s">
-        <v>265</v>
+        <v>229</v>
       </c>
       <c r="H23" t="s">
-        <v>264</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="B24" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="C24" s="1">
-        <v>46241.29166666667</v>
+        <v>46234.29166666667</v>
       </c>
       <c r="D24" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E24" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="F24" t="s">
-        <v>276</v>
+        <v>201</v>
       </c>
       <c r="G24" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="H24" t="s">
-        <v>34</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="B25" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C25" s="1">
-        <v>46245.29166666667</v>
+        <v>46234.29166666667</v>
       </c>
       <c r="D25" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E25" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F25" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G25" t="s">
-        <v>213</v>
+        <v>246</v>
       </c>
       <c r="H25" t="s">
-        <v>211</v>
+        <v>245</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="B26" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C26" s="1">
-        <v>46245.29166666667</v>
+        <v>46234.29166666667</v>
       </c>
       <c r="D26" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E26" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="F26" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G26" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="H26" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B27" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C27" s="1">
-        <v>46245.29166666667</v>
+        <v>46241.29166666667</v>
       </c>
       <c r="D27" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="E27" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="F27" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="G27" t="s">
-        <v>271</v>
+        <v>204</v>
       </c>
       <c r="H27" t="s">
-        <v>270</v>
+        <v>202</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="B28" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C28" s="1">
-        <v>46248.29166666667</v>
+        <v>46241.29166666667</v>
       </c>
       <c r="D28" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="E28" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="F28" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G28" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="H28" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="B29" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C29" s="1">
-        <v>46248.29166666667</v>
+        <v>46241.29166666667</v>
       </c>
       <c r="D29" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="E29" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="F29" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G29" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="H29" t="s">
-        <v>266</v>
+        <v>239</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="B30" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C30" s="1">
-        <v>46223.29166666667</v>
+        <v>46241.29166666667</v>
       </c>
       <c r="D30" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="E30" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="F30" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G30" t="s">
-        <v>206</v>
+        <v>244</v>
       </c>
       <c r="H30" t="s">
-        <v>204</v>
+        <v>243</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="B31" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C31" s="1">
-        <v>46223.29166666667</v>
+        <v>46241.29166666667</v>
       </c>
       <c r="D31" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="E31" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="F31" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G31" t="s">
-        <v>227</v>
+        <v>254</v>
       </c>
       <c r="H31" t="s">
-        <v>225</v>
+        <v>253</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="B32" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C32" s="1">
-        <v>46223.29166666667</v>
+        <v>46241.29166666667</v>
       </c>
       <c r="D32" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="E32" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="F32" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G32" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="H32" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="B33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C33" s="1">
-        <v>46223.29166666667</v>
+        <v>46241.29166666667</v>
       </c>
       <c r="D33" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="E33" t="s">
-        <v>136</v>
+        <v>171</v>
       </c>
       <c r="F33" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="G33" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="H33" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -5919,277 +6011,277 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B2">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B3">
         <v>645</v>
       </c>
       <c r="C3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B4">
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B5">
         <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B6">
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B7">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B8">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B15" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C15" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B16">
         <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="18" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B19" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C19" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B20" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C20" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B21" t="s">
         <v>316</v>
       </c>
       <c r="C21" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B22" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C22" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B23" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C23" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B24" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C24" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B25" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C25" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B26" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C26" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -6211,178 +6303,178 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C7" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B9" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C9" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B10" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C10" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B11" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C11" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B12" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C12" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B13" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C13" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B14" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C14" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B15" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C15" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C16" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>

--- a/samples/sample-records.xlsx
+++ b/samples/sample-records.xlsx
@@ -93,7 +93,7 @@
     <t>Reviewed by</t>
   </si>
   <si>
-    <t>1c34537e-6cd6-456b-957b-3cebf430d910</t>
+    <t>7db5ae9a-88ff-483b-b9ea-085d30ec4d35</t>
   </si>
   <si>
     <t>08:30</t>
@@ -138,7 +138,7 @@
     <t>Completed</t>
   </si>
   <si>
-    <t>22c36983-a5e0-4a01-94d3-844c35be481e</t>
+    <t>37fbc977-db9f-4372-a173-024fa6a6e323</t>
   </si>
   <si>
     <t>17:15</t>
@@ -174,7 +174,7 @@
     <t>Lt. C. Barnes</t>
   </si>
   <si>
-    <t>939b5190-a131-4843-9c4e-2dca8db97b40</t>
+    <t>c5784790-3b63-486e-8dec-4b52a41c8d09</t>
   </si>
   <si>
     <t>09:00</t>
@@ -204,7 +204,7 @@
     <t>Maintain double-blind cadence monthly</t>
   </si>
   <si>
-    <t>f0c810eb-f036-4968-aa6f-538fb32c82c5</t>
+    <t>f25afe84-7856-46d1-9a38-11d584cf1c62</t>
   </si>
   <si>
     <t>07:45</t>
@@ -228,7 +228,7 @@
     <t>Overcast, wind 5-10 mph from west</t>
   </si>
   <si>
-    <t>0d8bb97c-e8a0-4d01-b667-8fcf1d9ae789</t>
+    <t>7872ce6f-4fbf-4cf1-891f-a156d0caf004</t>
   </si>
   <si>
     <t>13:00</t>
@@ -249,7 +249,7 @@
     <t>Increase parcel line length; add moving-belt scenario when available</t>
   </si>
   <si>
-    <t>78b22f1d-daa6-484a-9760-1b2c33421082</t>
+    <t>48080c8e-2550-4fa3-8a25-5fb15df8fb6e</t>
   </si>
   <si>
     <t>10:00</t>
@@ -276,7 +276,7 @@
     <t>Schedule monthly shoreline maintenance; work under-deck airflow problems</t>
   </si>
   <si>
-    <t>ebf5ba77-6e92-4668-ab00-b077fe48be39</t>
+    <t>00d456de-f3ba-415f-b4bf-b5fd6a4a6e00</t>
   </si>
   <si>
     <t>08:15</t>
@@ -291,7 +291,7 @@
     <t>High-clutter environment with shelving to 12 ft. Cooper maintained drive throughout a long problem. Elevated SSD at 6 ft found via air scent cone. One false response near a shelf of seized electronics equipment (actual odor source plausible — logged as unconfirmed rather than false).</t>
   </si>
   <si>
-    <t>f608810e-df97-4c23-9cb6-bbda84773561</t>
+    <t>308ad22e-0824-4bee-ba15-3dcbd4bc5466</t>
   </si>
   <si>
     <t>09:30</t>
@@ -399,45 +399,87 @@
     <t>Comments</t>
   </si>
   <si>
-    <t>075d520b-9f13-4237-849e-1b1f0928f631</t>
+    <t>219b2aee-1290-4de3-bd17-e6340f0fc27f</t>
+  </si>
+  <si>
+    <t>Training boxes</t>
+  </si>
+  <si>
+    <t>Known hide</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>12-box line, one hot box</t>
+  </si>
+  <si>
+    <t>Sit (passive)</t>
+  </si>
+  <si>
+    <t>food</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>successful</t>
+  </si>
+  <si>
+    <t>475289ef-a0e8-4f67-91cf-74141d29caa2</t>
   </si>
   <si>
     <t>Room / building search</t>
   </si>
   <si>
+    <t>School / classroom</t>
+  </si>
+  <si>
+    <t>Double-blind</t>
+  </si>
+  <si>
+    <t>Four classrooms, east wing</t>
+  </si>
+  <si>
+    <t>Evaluator scored the run; handler had no knowledge of placements.</t>
+  </si>
+  <si>
+    <t>7ce5d377-2d15-4ab5-bb87-084baaf141a7</t>
+  </si>
+  <si>
+    <t>Parcel / luggage / mail</t>
+  </si>
+  <si>
+    <t>Single-blind</t>
+  </si>
+  <si>
+    <t>24-parcel line on rollers</t>
+  </si>
+  <si>
+    <t>Distractors: sealed food, cables, charger. Correct discrimination throughout.</t>
+  </si>
+  <si>
+    <t>879446c9-f7ca-4eec-8e12-77c8d59dd432</t>
+  </si>
+  <si>
     <t>Office</t>
   </si>
   <si>
-    <t>Single-blind</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>Three connected offices, second floor</t>
   </si>
   <si>
-    <t>Sit (passive)</t>
-  </si>
-  <si>
-    <t>food</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>successful</t>
-  </si>
-  <si>
-    <t>24ba8f0f-63c0-4110-b068-136e3581bce9</t>
+    <t>8b3b7de7-2b44-4143-8d94-4df53024d621</t>
+  </si>
+  <si>
+    <t>12-box line, six hot boxes run sequentially</t>
+  </si>
+  <si>
+    <t>901b00a9-04d6-45e9-8280-42376ffe3de9</t>
   </si>
   <si>
     <t>Water / shoreline</t>
   </si>
   <si>
-    <t>Known hide</t>
-  </si>
-  <si>
     <t>Dock and shoreline, ~80 yards</t>
   </si>
   <si>
@@ -447,22 +489,43 @@
     <t>Onshore wind pushed odor under decking; discussed presentation options.</t>
   </si>
   <si>
-    <t>86c79adf-8fdd-4524-84c4-1143a57beec0</t>
-  </si>
-  <si>
-    <t>Training boxes</t>
-  </si>
-  <si>
-    <t>12-box line, one hot box</t>
-  </si>
-  <si>
-    <t>9d14f059-7739-4904-8b66-77ea53ef1627</t>
-  </si>
-  <si>
-    <t>12-box line, six hot boxes run sequentially</t>
-  </si>
-  <si>
-    <t>b14fdb3f-3a1a-4f5b-8f62-7cef7224606c</t>
+    <t>ab668373-d6ea-4dd5-aeea-7ef05340bb83</t>
+  </si>
+  <si>
+    <t>Outdoor / open area</t>
+  </si>
+  <si>
+    <t>Tree line and picnic area, ~100 x 40 yards</t>
+  </si>
+  <si>
+    <t>Worked crosswind pattern; off-leash under voice control.</t>
+  </si>
+  <si>
+    <t>b148615a-251f-49c9-ad71-6656a70f0366</t>
+  </si>
+  <si>
+    <t>Cluttered environment</t>
+  </si>
+  <si>
+    <t>Warehouse</t>
+  </si>
+  <si>
+    <t>Warehouse floor, aisles A-D</t>
+  </si>
+  <si>
+    <t>c1b976cb-7d1b-446d-9545-7739432579b2</t>
+  </si>
+  <si>
+    <t>Vehicle search</t>
+  </si>
+  <si>
+    <t>Four sedans, parking level 1</t>
+  </si>
+  <si>
+    <t>Heat affected later runs; added rest and water breaks between vehicles.</t>
+  </si>
+  <si>
+    <t>c662be51-628d-4f30-b111-dc8f8aa06b68</t>
   </si>
   <si>
     <t>Blank / negative search</t>
@@ -477,69 +540,6 @@
     <t>Clean blank. No interest shown, handler called the room clear.</t>
   </si>
   <si>
-    <t>b33e0638-0cdf-49d2-8501-dbb14a82726a</t>
-  </si>
-  <si>
-    <t>Cluttered environment</t>
-  </si>
-  <si>
-    <t>Warehouse</t>
-  </si>
-  <si>
-    <t>Warehouse floor, aisles A-D</t>
-  </si>
-  <si>
-    <t>db330657-7c1e-4d7e-a868-5ac8020ee662</t>
-  </si>
-  <si>
-    <t>Vehicle search</t>
-  </si>
-  <si>
-    <t>Four sedans, parking level 1</t>
-  </si>
-  <si>
-    <t>Heat affected later runs; added rest and water breaks between vehicles.</t>
-  </si>
-  <si>
-    <t>eaead4ef-2765-4155-b46e-14a1d575d146</t>
-  </si>
-  <si>
-    <t>Outdoor / open area</t>
-  </si>
-  <si>
-    <t>Tree line and picnic area, ~100 x 40 yards</t>
-  </si>
-  <si>
-    <t>Worked crosswind pattern; off-leash under voice control.</t>
-  </si>
-  <si>
-    <t>ee3a38cc-f66b-4c43-9bf1-18e38757da4e</t>
-  </si>
-  <si>
-    <t>Parcel / luggage / mail</t>
-  </si>
-  <si>
-    <t>24-parcel line on rollers</t>
-  </si>
-  <si>
-    <t>Distractors: sealed food, cables, charger. Correct discrimination throughout.</t>
-  </si>
-  <si>
-    <t>fdbf140d-dea5-4e43-b360-50eb2da880b6</t>
-  </si>
-  <si>
-    <t>School / classroom</t>
-  </si>
-  <si>
-    <t>Double-blind</t>
-  </si>
-  <si>
-    <t>Four classrooms, east wing</t>
-  </si>
-  <si>
-    <t>Evaluator scored the run; handler had no knowledge of placements.</t>
-  </si>
-  <si>
     <t>Hide ID</t>
   </si>
   <si>
@@ -588,43 +588,205 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>05ed2830-029c-452f-93c6-db70e3a33fff</t>
+    <t>05b652d1-0cba-4688-8126-0504ad11d8e2</t>
   </si>
   <si>
     <t>Electronic storage device</t>
   </si>
   <si>
+    <t>SD card</t>
+  </si>
+  <si>
+    <t>Parcel 14, inside greeting card</t>
+  </si>
+  <si>
+    <t>fully concealed</t>
+  </si>
+  <si>
+    <t>Found — independent</t>
+  </si>
+  <si>
+    <t>07ce5ed2-36f1-4757-a052-4376a4415f29</t>
+  </si>
+  <si>
+    <t>Cellphone</t>
+  </si>
+  <si>
+    <t>Box 2</t>
+  </si>
+  <si>
+    <t>1d766083-d317-4549-bb5a-b292b963a1e2</t>
+  </si>
+  <si>
+    <t>MicroSD card</t>
+  </si>
+  <si>
+    <t>Library, inside hollowed book</t>
+  </si>
+  <si>
+    <t>chest</t>
+  </si>
+  <si>
+    <t>33413c1c-6a05-48cc-8a6e-d31f3279aa2e</t>
+  </si>
+  <si>
     <t>USB drive</t>
   </si>
   <si>
+    <t>Buried ~4 in. at base of oak, marked GPS</t>
+  </si>
+  <si>
+    <t>floor</t>
+  </si>
+  <si>
+    <t>buried</t>
+  </si>
+  <si>
+    <t>334598f3-0dff-48b1-8a78-e073ec2d2213</t>
+  </si>
+  <si>
+    <t>Classroom 4, pencil box in desk</t>
+  </si>
+  <si>
+    <t>waist</t>
+  </si>
+  <si>
+    <t>433ea336-0506-489b-8fec-b8e8055807b1</t>
+  </si>
+  <si>
+    <t>Inside rolled carpet, aisle D</t>
+  </si>
+  <si>
+    <t>4779a2b4-8b3d-4f4c-b17e-a857d3a2d6cd</t>
+  </si>
+  <si>
+    <t>Parcel 6, wrapped in clothing</t>
+  </si>
+  <si>
+    <t>532033ab-c93a-4159-8eff-e4769473ce1a</t>
+  </si>
+  <si>
+    <t>Box 11</t>
+  </si>
+  <si>
+    <t>6496fdb4-c23c-431b-a7da-7a68dfcf4b2f</t>
+  </si>
+  <si>
+    <t>Hard drive</t>
+  </si>
+  <si>
+    <t>Box 9 (second run)</t>
+  </si>
+  <si>
+    <t>6bb37975-0197-43eb-97d9-76c7f527f16a</t>
+  </si>
+  <si>
+    <t>SIM card</t>
+  </si>
+  <si>
+    <t>Box 3 (second run)</t>
+  </si>
+  <si>
+    <t>70084e97-40c1-42f4-8a7b-842af4093da5</t>
+  </si>
+  <si>
+    <t>Glove box, vehicle 4</t>
+  </si>
+  <si>
+    <t>7ccbea13-ad82-4f2a-b6ba-c7741c198da6</t>
+  </si>
+  <si>
+    <t>Classroom 3, bookshelf, third shelf</t>
+  </si>
+  <si>
+    <t>partially concealed</t>
+  </si>
+  <si>
+    <t>826365cb-cabd-4fd8-9416-45ba6ac8e89b</t>
+  </si>
+  <si>
+    <t>Parcel 9 (residual — phone removed prior day)</t>
+  </si>
+  <si>
+    <t>Interest, no indication</t>
+  </si>
+  <si>
+    <t>Interest only, no final response; treated as correct discrimination of residual odor</t>
+  </si>
+  <si>
+    <t>8ba76399-0f81-407d-ba1f-5cf87722d52f</t>
+  </si>
+  <si>
+    <t>Box 5</t>
+  </si>
+  <si>
+    <t>8dab30b1-1f3f-406b-ba09-c0c21ac1e337</t>
+  </si>
+  <si>
+    <t>Desk drawer, second from top</t>
+  </si>
+  <si>
+    <t>8e321a66-8f89-4ae6-a193-0ca345c54a21</t>
+  </si>
+  <si>
+    <t>Behind loose baseboard, north wall</t>
+  </si>
+  <si>
+    <t>Required second pass; committed final response, no cue given</t>
+  </si>
+  <si>
+    <t>9da386e5-700e-4d57-8df1-09763ae3b438</t>
+  </si>
+  <si>
+    <t>Classroom 5, taped under chair</t>
+  </si>
+  <si>
+    <t>knee</t>
+  </si>
+  <si>
+    <t>9f3caa20-0251-4529-9807-a94581bba462</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>Aisle B, shelf at ~6 ft</t>
+  </si>
+  <si>
+    <t>elevated</t>
+  </si>
+  <si>
+    <t>a7e16c8a-287e-4cf4-b56f-916df477a22f</t>
+  </si>
+  <si>
+    <t>Box 7 of 12</t>
+  </si>
+  <si>
+    <t>bef25d9c-316c-4948-8f43-46118f824e13</t>
+  </si>
+  <si>
+    <t>Dry bag at waterline piling</t>
+  </si>
+  <si>
+    <t>c2393805-528b-4fdf-a6f1-9ec1a768f783</t>
+  </si>
+  <si>
+    <t>Box 8</t>
+  </si>
+  <si>
+    <t>c2e45910-fb6a-4fba-8e1c-9fb8827dc72a</t>
+  </si>
+  <si>
     <t>Taped under dock decking, mid-span</t>
   </si>
   <si>
-    <t>floor</t>
-  </si>
-  <si>
-    <t>fully concealed</t>
-  </si>
-  <si>
     <t>Found — handler assisted</t>
   </si>
   <si>
     <t>Directed recheck after first pass; correct response on presentation</t>
   </si>
   <si>
-    <t>0d0bf1c5-917f-4462-8dc9-00574a8b48be</t>
-  </si>
-  <si>
-    <t>SD card</t>
-  </si>
-  <si>
-    <t>Box 5</t>
-  </si>
-  <si>
-    <t>Found — independent</t>
-  </si>
-  <si>
-    <t>105bb7eb-6b03-431a-870b-829f51ff43af</t>
+    <t>c3c375ba-afa0-4aa4-a96b-6226f5edd26a</t>
   </si>
   <si>
     <t>Tablet</t>
@@ -633,216 +795,54 @@
     <t>Teacher lounge, locker 12</t>
   </si>
   <si>
-    <t>chest</t>
-  </si>
-  <si>
     <t>Missed</t>
   </si>
   <si>
     <t>Locker vents faced away from aisle; airflow discussed with evaluator</t>
   </si>
   <si>
-    <t>16abf7ba-9ab5-45b0-9be3-817a903ec215</t>
-  </si>
-  <si>
-    <t>SIM card</t>
+    <t>c576722f-fbd1-46d7-8a13-f8951ce35e6b</t>
+  </si>
+  <si>
+    <t>Pill bottle inside toolbox, aisle A</t>
+  </si>
+  <si>
+    <t>d18d93f1-44c3-40f4-8da3-e2911ed829da</t>
+  </si>
+  <si>
+    <t>Library AV closet, top shelf</t>
+  </si>
+  <si>
+    <t>Elevated hide — good air scenting</t>
+  </si>
+  <si>
+    <t>d415c888-781c-462a-b621-c24b475da557</t>
+  </si>
+  <si>
+    <t>Under driver seat, vehicle 1</t>
+  </si>
+  <si>
+    <t>d7681d1f-9bfa-459c-80b9-a289c04c0f10</t>
+  </si>
+  <si>
+    <t>Under park bench slat</t>
+  </si>
+  <si>
+    <t>e8efe195-3f3b-4555-9a3c-51028cd4eac5</t>
   </si>
   <si>
     <t>Magnet box, rear wheel well, vehicle 3</t>
   </si>
   <si>
-    <t>knee</t>
-  </si>
-  <si>
     <t>Missed on first pass; found on re-run with handler presenting the wheel well</t>
   </si>
   <si>
-    <t>2089b8bf-7329-464b-97cb-aa777434e3de</t>
-  </si>
-  <si>
-    <t>Box 11</t>
-  </si>
-  <si>
-    <t>229490a4-9040-4184-aaeb-3307c8a88109</t>
-  </si>
-  <si>
-    <t>MicroSD card</t>
-  </si>
-  <si>
-    <t>Box 8</t>
-  </si>
-  <si>
-    <t>37793846-4bd7-41bf-9c2c-e41d2d9d6efb</t>
-  </si>
-  <si>
-    <t>Hard drive</t>
-  </si>
-  <si>
-    <t>Library AV closet, top shelf</t>
-  </si>
-  <si>
-    <t>elevated</t>
-  </si>
-  <si>
-    <t>partially concealed</t>
-  </si>
-  <si>
-    <t>Elevated hide — good air scenting</t>
-  </si>
-  <si>
-    <t>459809df-f05d-4f50-9d79-c46802b4f87c</t>
-  </si>
-  <si>
-    <t>SSD</t>
-  </si>
-  <si>
-    <t>Aisle B, shelf at ~6 ft</t>
-  </si>
-  <si>
-    <t>4bd8b650-373e-4322-a0b7-41ed157aee22</t>
-  </si>
-  <si>
-    <t>Cellphone</t>
-  </si>
-  <si>
-    <t>Parcel 9 (residual — phone removed prior day)</t>
-  </si>
-  <si>
-    <t>Interest, no indication</t>
-  </si>
-  <si>
-    <t>Interest only, no final response; treated as correct discrimination of residual odor</t>
-  </si>
-  <si>
-    <t>4e465b85-899c-49cf-b1f5-087b3fa03ee9</t>
-  </si>
-  <si>
-    <t>Parcel 6, wrapped in clothing</t>
-  </si>
-  <si>
-    <t>6232cdfb-edf6-40fe-8a74-871f2a26bd28</t>
-  </si>
-  <si>
-    <t>Pill bottle inside toolbox, aisle A</t>
-  </si>
-  <si>
-    <t>waist</t>
-  </si>
-  <si>
-    <t>6404447e-8e5a-47b0-9faf-65040d768772</t>
-  </si>
-  <si>
-    <t>Desk drawer, second from top</t>
-  </si>
-  <si>
-    <t>6cb163f3-a5c9-421f-b4dc-9d4517ed38b9</t>
-  </si>
-  <si>
-    <t>Classroom 3, bookshelf, third shelf</t>
-  </si>
-  <si>
-    <t>75034a3f-e137-4171-a366-d5ced551169d</t>
-  </si>
-  <si>
-    <t>Box 9 (second run)</t>
-  </si>
-  <si>
-    <t>76f6e59e-30d2-41ff-a926-a161e4e8ed2d</t>
-  </si>
-  <si>
-    <t>Classroom 4, pencil box in desk</t>
-  </si>
-  <si>
-    <t>77c613b1-d684-4446-9e35-2c8e5d8c5e8e</t>
-  </si>
-  <si>
-    <t>Parcel 14, inside greeting card</t>
-  </si>
-  <si>
-    <t>790245ae-1b44-44f6-a389-c789576a9101</t>
+    <t>f61b12c4-a913-4db5-8db1-78f4fdb39d59</t>
   </si>
   <si>
     <t>Parcel 21, boxed with packing foam</t>
   </si>
   <si>
-    <t>7f399786-9f9f-4446-b1a2-0224a87d6e7a</t>
-  </si>
-  <si>
-    <t>Under driver seat, vehicle 1</t>
-  </si>
-  <si>
-    <t>88c9fd69-f9aa-439e-a88f-fc789b2d1b41</t>
-  </si>
-  <si>
-    <t>Box 7 of 12</t>
-  </si>
-  <si>
-    <t>9964ece3-92ab-4b79-af44-5ebd42044fe7</t>
-  </si>
-  <si>
-    <t>Classroom 5, taped under chair</t>
-  </si>
-  <si>
-    <t>a36502d5-84b0-44a8-8f51-a606b37e4dfa</t>
-  </si>
-  <si>
-    <t>Library, inside hollowed book</t>
-  </si>
-  <si>
-    <t>a786eea6-e619-4630-b850-a9ca0286f544</t>
-  </si>
-  <si>
-    <t>Inside rolled carpet, aisle D</t>
-  </si>
-  <si>
-    <t>c53c6500-17ce-4931-8833-acd27e17b544</t>
-  </si>
-  <si>
-    <t>Dry bag at waterline piling</t>
-  </si>
-  <si>
-    <t>dcb0438f-12ba-4185-bbdd-339d1736db87</t>
-  </si>
-  <si>
-    <t>Glove box, vehicle 4</t>
-  </si>
-  <si>
-    <t>e28b04be-7247-4eae-a4a5-401d168e9ccf</t>
-  </si>
-  <si>
-    <t>Box 2</t>
-  </si>
-  <si>
-    <t>e426f2d9-4174-410b-8c07-ab49975a35b6</t>
-  </si>
-  <si>
-    <t>Box 3 (second run)</t>
-  </si>
-  <si>
-    <t>ebde832a-8822-495b-84d6-6b5c03fcd7c3</t>
-  </si>
-  <si>
-    <t>Behind loose baseboard, north wall</t>
-  </si>
-  <si>
-    <t>Required second pass; committed final response, no cue given</t>
-  </si>
-  <si>
-    <t>fa044aec-bbb2-42bf-9c6f-e62bc4d5da28</t>
-  </si>
-  <si>
-    <t>Buried ~4 in. at base of oak, marked GPS</t>
-  </si>
-  <si>
-    <t>buried</t>
-  </si>
-  <si>
-    <t>fb6c08c6-82cb-4e9e-874f-046636d6db89</t>
-  </si>
-  <si>
-    <t>Under park bench slat</t>
-  </si>
-  <si>
     <t>Outcome category</t>
   </si>
   <si>
@@ -852,18 +852,18 @@
     <t>Related hide ID</t>
   </si>
   <si>
+    <t>False response</t>
+  </si>
+  <si>
+    <t>Cafeteria storage cabinet — suspected cause: Suspected residual odor — cabinet previously stored tablets</t>
+  </si>
+  <si>
+    <t>Aisle C, shelf of seized AV equipment — suspected cause: Unconfirmed — possible actual storage media within sealed evidence; could not verify</t>
+  </si>
+  <si>
     <t>Blank search — correct clear</t>
   </si>
   <si>
-    <t>False response</t>
-  </si>
-  <si>
-    <t>Aisle C, shelf of seized AV equipment — suspected cause: Unconfirmed — possible actual storage media within sealed evidence; could not verify</t>
-  </si>
-  <si>
-    <t>Cafeteria storage cabinet — suspected cause: Suspected residual odor — cabinet previously stored tablets</t>
-  </si>
-  <si>
     <t>Metric</t>
   </si>
   <si>
@@ -963,58 +963,58 @@
     <t>By search type</t>
   </si>
   <si>
+    <t xml:space="preserve">  Training boxes</t>
+  </si>
+  <si>
+    <t>2 exercises</t>
+  </si>
+  <si>
+    <t>7 hides, 7 finds, 0 misses. Last practiced 2026-08-14.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  Room / building search</t>
   </si>
   <si>
-    <t>2 exercises</t>
-  </si>
-  <si>
     <t>8 hides, 7 finds, 1 misses. Last practiced 2026-08-14.</t>
   </si>
   <si>
+    <t xml:space="preserve">  Parcel / luggage / mail</t>
+  </si>
+  <si>
+    <t>1 exercises</t>
+  </si>
+  <si>
+    <t>4 hides, 3 finds, 0 misses. Last practiced 2026-07-31.</t>
+  </si>
+  <si>
     <t xml:space="preserve">  Water / shoreline</t>
   </si>
   <si>
-    <t>1 exercises</t>
-  </si>
-  <si>
     <t>2 hides, 2 finds, 0 misses. Last practiced 2026-07-27.</t>
   </si>
   <si>
-    <t xml:space="preserve">  Training boxes</t>
-  </si>
-  <si>
-    <t>7 hides, 7 finds, 0 misses. Last practiced 2026-08-14.</t>
+    <t xml:space="preserve">  Outdoor / open area</t>
+  </si>
+  <si>
+    <t>2 hides, 2 finds, 0 misses. Last practiced 2026-08-04.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Cluttered environment</t>
+  </si>
+  <si>
+    <t>3 hides, 3 finds, 0 misses. Last practiced 2026-07-20.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Vehicle search</t>
+  </si>
+  <si>
+    <t>3 hides, 2 finds, 1 misses. Last practiced 2026-08-11.</t>
   </si>
   <si>
     <t xml:space="preserve">  Blank / negative search</t>
   </si>
   <si>
     <t>0 hides, 0 finds, 0 misses. Last practiced 2026-08-14.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Cluttered environment</t>
-  </si>
-  <si>
-    <t>3 hides, 3 finds, 0 misses. Last practiced 2026-07-20.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Vehicle search</t>
-  </si>
-  <si>
-    <t>3 hides, 2 finds, 1 misses. Last practiced 2026-08-11.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Outdoor / open area</t>
-  </si>
-  <si>
-    <t>2 hides, 2 finds, 0 misses. Last practiced 2026-08-04.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Parcel / luggage / mail</t>
-  </si>
-  <si>
-    <t>4 hides, 3 finds, 0 misses. Last practiced 2026-07-31.</t>
   </si>
   <si>
     <t>Sheet</t>
@@ -1652,10 +1652,10 @@
         <v>39</v>
       </c>
       <c r="W2" s="2">
-        <v>46251.19757380787</v>
+        <v>46251.21739293981</v>
       </c>
       <c r="X2" s="2">
-        <v>46251.19757380787</v>
+        <v>46251.21739293981</v>
       </c>
       <c r="Y2" t="s">
         <v>30</v>
@@ -1729,10 +1729,10 @@
         <v>50</v>
       </c>
       <c r="W3" s="2">
-        <v>46251.1975738426</v>
+        <v>46251.217392997685</v>
       </c>
       <c r="X3" s="2">
-        <v>46251.1975738426</v>
+        <v>46251.217392997685</v>
       </c>
       <c r="Y3" t="s">
         <v>51</v>
@@ -1806,10 +1806,10 @@
         <v>50</v>
       </c>
       <c r="W4" s="2">
-        <v>46251.19757386574</v>
+        <v>46251.21739305556</v>
       </c>
       <c r="X4" s="2">
-        <v>46251.19757386574</v>
+        <v>46251.21739305556</v>
       </c>
       <c r="Y4" t="s">
         <v>51</v>
@@ -1883,10 +1883,10 @@
         <v>39</v>
       </c>
       <c r="W5" s="2">
-        <v>46251.19757388889</v>
+        <v>46251.2173930787</v>
       </c>
       <c r="X5" s="2">
-        <v>46251.19757388889</v>
+        <v>46251.2173930787</v>
       </c>
       <c r="Y5" t="s">
         <v>30</v>
@@ -1960,10 +1960,10 @@
         <v>39</v>
       </c>
       <c r="W6" s="2">
-        <v>46251.19757390046</v>
+        <v>46251.21739309028</v>
       </c>
       <c r="X6" s="2">
-        <v>46251.19757390046</v>
+        <v>46251.21739309028</v>
       </c>
       <c r="Y6" t="s">
         <v>30</v>
@@ -2037,10 +2037,10 @@
         <v>39</v>
       </c>
       <c r="W7" s="2">
-        <v>46251.19757392361</v>
+        <v>46251.21739311343</v>
       </c>
       <c r="X7" s="2">
-        <v>46251.19757392361</v>
+        <v>46251.21739311343</v>
       </c>
       <c r="Y7" t="s">
         <v>30</v>
@@ -2114,10 +2114,10 @@
         <v>39</v>
       </c>
       <c r="W8" s="2">
-        <v>46251.197573935184</v>
+        <v>46251.217393125</v>
       </c>
       <c r="X8" s="2">
-        <v>46251.197573935184</v>
+        <v>46251.217393125</v>
       </c>
       <c r="Y8" t="s">
         <v>30</v>
@@ -2191,10 +2191,10 @@
         <v>39</v>
       </c>
       <c r="W9" s="2">
-        <v>46251.19757394676</v>
+        <v>46251.21739313657</v>
       </c>
       <c r="X9" s="2">
-        <v>46251.19757394676</v>
+        <v>46251.21739313657</v>
       </c>
       <c r="Y9" t="s">
         <v>30</v>
@@ -2345,31 +2345,31 @@
         <v>46248.29166666667</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
         <v>128</v>
       </c>
       <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
         <v>129</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>130</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" t="s">
         <v>131</v>
       </c>
-      <c r="I2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" t="s">
-        <v>132</v>
-      </c>
       <c r="K2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -2378,49 +2378,49 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>540</v>
+        <v>120</v>
       </c>
       <c r="P2">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="Q2" t="s">
-        <v>131</v>
-      </c>
-      <c r="R2">
+        <v>130</v>
+      </c>
+      <c r="R2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S2">
+        <v>5</v>
+      </c>
+      <c r="T2" t="s">
+        <v>30</v>
+      </c>
+      <c r="U2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V2" t="s">
+        <v>30</v>
+      </c>
+      <c r="W2">
         <v>4</v>
       </c>
-      <c r="S2">
-        <v>4</v>
-      </c>
-      <c r="T2">
-        <v>5</v>
-      </c>
-      <c r="U2">
-        <v>4</v>
-      </c>
-      <c r="V2" t="s">
-        <v>30</v>
-      </c>
-      <c r="W2">
-        <v>5</v>
-      </c>
       <c r="X2" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z2" t="s">
         <v>133</v>
       </c>
-      <c r="Y2" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z2" t="s">
+      <c r="AA2">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="s">
         <v>134</v>
       </c>
-      <c r="AA2">
-        <v>2</v>
-      </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>135</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>136</v>
       </c>
       <c r="AD2" t="s">
         <v>30</v>
@@ -2434,28 +2434,28 @@
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="C3" s="1">
-        <v>46230.29166666667</v>
+        <v>46241.29166666667</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F3" t="s">
         <v>138</v>
-      </c>
-      <c r="F3" t="s">
-        <v>30</v>
       </c>
       <c r="G3" t="s">
         <v>139</v>
       </c>
       <c r="H3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I3" t="s">
         <v>30</v>
@@ -2464,96 +2464,96 @@
         <v>140</v>
       </c>
       <c r="K3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3">
-        <v>720</v>
+        <v>1500</v>
       </c>
       <c r="P3">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="Q3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S3">
         <v>4</v>
       </c>
       <c r="T3">
+        <v>5</v>
+      </c>
+      <c r="U3">
+        <v>4</v>
+      </c>
+      <c r="V3">
+        <v>4</v>
+      </c>
+      <c r="W3">
+        <v>5</v>
+      </c>
+      <c r="X3" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AA3">
         <v>3</v>
       </c>
-      <c r="U3" t="s">
-        <v>30</v>
-      </c>
-      <c r="V3" t="s">
-        <v>30</v>
-      </c>
-      <c r="W3">
-        <v>4</v>
-      </c>
-      <c r="X3" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z3" t="s">
+      <c r="AB3" t="s">
         <v>134</v>
       </c>
-      <c r="AA3">
-        <v>2</v>
-      </c>
-      <c r="AB3" t="s">
+      <c r="AC3" t="s">
         <v>135</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AD3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF3" t="s">
         <v>141</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="1">
+        <v>46234.29166666667</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
         <v>143</v>
       </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="1">
-        <v>46248.29166666667</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
         <v>144</v>
       </c>
-      <c r="F4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" t="s">
-        <v>139</v>
-      </c>
       <c r="H4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I4" t="s">
         <v>30</v>
@@ -2562,10 +2562,10 @@
         <v>145</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -2574,25 +2574,25 @@
         <v>0</v>
       </c>
       <c r="O4">
-        <v>120</v>
+        <v>600</v>
       </c>
       <c r="P4">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="Q4" t="s">
-        <v>131</v>
-      </c>
-      <c r="R4" t="s">
-        <v>30</v>
+        <v>130</v>
+      </c>
+      <c r="R4">
+        <v>4</v>
       </c>
       <c r="S4">
+        <v>4</v>
+      </c>
+      <c r="T4">
+        <v>4</v>
+      </c>
+      <c r="U4">
         <v>5</v>
-      </c>
-      <c r="T4" t="s">
-        <v>30</v>
-      </c>
-      <c r="U4" t="s">
-        <v>30</v>
       </c>
       <c r="V4" t="s">
         <v>30</v>
@@ -2601,23 +2601,23 @@
         <v>4</v>
       </c>
       <c r="X4" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z4" t="s">
         <v>133</v>
       </c>
-      <c r="Y4" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z4" t="s">
+      <c r="AA4">
+        <v>3</v>
+      </c>
+      <c r="AB4" t="s">
         <v>134</v>
       </c>
-      <c r="AA4">
-        <v>1</v>
-      </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>135</v>
       </c>
-      <c r="AC4" t="s">
-        <v>136</v>
-      </c>
       <c r="AD4" t="s">
         <v>30</v>
       </c>
@@ -2625,45 +2625,45 @@
         <v>30</v>
       </c>
       <c r="AF4" t="s">
-        <v>30</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1">
-        <v>46216.29166666667</v>
+        <v>46248.29166666667</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F5" t="s">
+        <v>148</v>
+      </c>
+      <c r="G5" t="s">
         <v>144</v>
       </c>
-      <c r="F5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>130</v>
       </c>
-      <c r="H5" t="s">
-        <v>131</v>
-      </c>
       <c r="I5" t="s">
         <v>30</v>
       </c>
       <c r="J5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -2672,25 +2672,25 @@
         <v>0</v>
       </c>
       <c r="O5">
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="P5">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="Q5" t="s">
-        <v>131</v>
-      </c>
-      <c r="R5" t="s">
-        <v>30</v>
+        <v>130</v>
+      </c>
+      <c r="R5">
+        <v>4</v>
       </c>
       <c r="S5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5">
         <v>5</v>
       </c>
-      <c r="U5" t="s">
-        <v>30</v>
+      <c r="U5">
+        <v>4</v>
       </c>
       <c r="V5" t="s">
         <v>30</v>
@@ -2699,22 +2699,22 @@
         <v>5</v>
       </c>
       <c r="X5" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z5" t="s">
         <v>133</v>
       </c>
-      <c r="Y5" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z5" t="s">
+      <c r="AA5">
+        <v>2</v>
+      </c>
+      <c r="AB5" t="s">
         <v>134</v>
       </c>
-      <c r="AA5">
-        <v>4</v>
-      </c>
-      <c r="AB5" t="s">
+      <c r="AC5" t="s">
         <v>135</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>136</v>
       </c>
       <c r="AD5" t="s">
         <v>30</v>
@@ -2728,40 +2728,40 @@
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="C6" s="1">
-        <v>46248.29166666667</v>
+        <v>46216.29166666667</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="F6" t="s">
-        <v>129</v>
+        <v>30</v>
       </c>
       <c r="G6" t="s">
+        <v>144</v>
+      </c>
+      <c r="H6" t="s">
         <v>130</v>
       </c>
-      <c r="H6" t="s">
-        <v>135</v>
-      </c>
       <c r="I6" t="s">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="J6" t="s">
         <v>151</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -2770,49 +2770,49 @@
         <v>0</v>
       </c>
       <c r="O6">
-        <v>240</v>
-      </c>
-      <c r="P6" t="s">
+        <v>480</v>
+      </c>
+      <c r="P6">
         <v>30</v>
       </c>
       <c r="Q6" t="s">
-        <v>131</v>
-      </c>
-      <c r="R6">
+        <v>130</v>
+      </c>
+      <c r="R6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S6">
+        <v>5</v>
+      </c>
+      <c r="T6">
+        <v>5</v>
+      </c>
+      <c r="U6" t="s">
+        <v>30</v>
+      </c>
+      <c r="V6" t="s">
+        <v>30</v>
+      </c>
+      <c r="W6">
+        <v>5</v>
+      </c>
+      <c r="X6" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>133</v>
+      </c>
+      <c r="AA6">
         <v>4</v>
       </c>
-      <c r="S6" t="s">
-        <v>30</v>
-      </c>
-      <c r="T6" t="s">
-        <v>30</v>
-      </c>
-      <c r="U6">
-        <v>4</v>
-      </c>
-      <c r="V6" t="s">
-        <v>30</v>
-      </c>
-      <c r="W6" t="s">
-        <v>30</v>
-      </c>
-      <c r="X6" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z6" t="s">
+      <c r="AB6" t="s">
         <v>134</v>
       </c>
-      <c r="AA6" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>30</v>
-      </c>
       <c r="AC6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AD6" t="s">
         <v>30</v>
@@ -2821,96 +2821,96 @@
         <v>30</v>
       </c>
       <c r="AF6" t="s">
-        <v>152</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C7" s="1">
-        <v>46223.29166666667</v>
+        <v>46230.29166666667</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" t="s">
+        <v>129</v>
+      </c>
+      <c r="H7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" t="s">
         <v>154</v>
       </c>
-      <c r="F7" t="s">
-        <v>155</v>
-      </c>
-      <c r="G7" t="s">
-        <v>130</v>
-      </c>
-      <c r="H7" t="s">
-        <v>131</v>
-      </c>
-      <c r="I7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" t="s">
-        <v>156</v>
-      </c>
       <c r="K7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M7">
         <v>0</v>
       </c>
       <c r="N7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>1800</v>
+        <v>720</v>
       </c>
       <c r="P7">
-        <v>320</v>
+        <v>180</v>
       </c>
       <c r="Q7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S7">
         <v>4</v>
       </c>
       <c r="T7">
-        <v>4</v>
-      </c>
-      <c r="U7">
-        <v>4</v>
-      </c>
-      <c r="V7">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="U7" t="s">
+        <v>30</v>
+      </c>
+      <c r="V7" t="s">
+        <v>30</v>
       </c>
       <c r="W7">
         <v>4</v>
       </c>
       <c r="X7" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z7" t="s">
         <v>133</v>
       </c>
-      <c r="Y7" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z7" t="s">
+      <c r="AA7">
+        <v>2</v>
+      </c>
+      <c r="AB7" t="s">
         <v>134</v>
       </c>
-      <c r="AA7">
-        <v>3</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>135</v>
-      </c>
       <c r="AC7" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="AD7" t="s">
         <v>30</v>
@@ -2919,7 +2919,7 @@
         <v>30</v>
       </c>
       <c r="AF7" t="s">
-        <v>30</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -2927,10 +2927,10 @@
         <v>157</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="C8" s="1">
-        <v>46245.29166666667</v>
+        <v>46238.29166666667</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -2942,10 +2942,10 @@
         <v>30</v>
       </c>
       <c r="G8" t="s">
+        <v>129</v>
+      </c>
+      <c r="H8" t="s">
         <v>130</v>
-      </c>
-      <c r="H8" t="s">
-        <v>131</v>
       </c>
       <c r="I8" t="s">
         <v>30</v>
@@ -2954,61 +2954,61 @@
         <v>159</v>
       </c>
       <c r="K8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L8">
         <v>2</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <v>0</v>
       </c>
       <c r="O8">
-        <v>780</v>
+        <v>900</v>
       </c>
       <c r="P8">
+        <v>260</v>
+      </c>
+      <c r="Q8" t="s">
         <v>130</v>
       </c>
-      <c r="Q8" t="s">
-        <v>131</v>
-      </c>
       <c r="R8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U8" t="s">
         <v>30</v>
       </c>
       <c r="V8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W8">
         <v>4</v>
       </c>
       <c r="X8" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z8" t="s">
         <v>133</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>134</v>
       </c>
       <c r="AA8">
         <v>2</v>
       </c>
       <c r="AB8" t="s">
+        <v>134</v>
+      </c>
+      <c r="AC8" t="s">
         <v>135</v>
-      </c>
-      <c r="AC8" t="s">
-        <v>141</v>
       </c>
       <c r="AD8" t="s">
         <v>30</v>
@@ -3025,10 +3025,10 @@
         <v>161</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="C9" s="1">
-        <v>46238.29166666667</v>
+        <v>46223.29166666667</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -3037,77 +3037,77 @@
         <v>162</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>163</v>
       </c>
       <c r="G9" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="H9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I9" t="s">
         <v>30</v>
       </c>
       <c r="J9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M9">
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="P9">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="Q9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R9">
         <v>4</v>
       </c>
       <c r="S9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T9">
-        <v>5</v>
-      </c>
-      <c r="U9" t="s">
-        <v>30</v>
+        <v>4</v>
+      </c>
+      <c r="U9">
+        <v>4</v>
       </c>
       <c r="V9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W9">
         <v>4</v>
       </c>
       <c r="X9" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z9" t="s">
         <v>133</v>
       </c>
-      <c r="Y9" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z9" t="s">
+      <c r="AA9">
+        <v>3</v>
+      </c>
+      <c r="AB9" t="s">
         <v>134</v>
       </c>
-      <c r="AA9">
-        <v>2</v>
-      </c>
-      <c r="AB9" t="s">
+      <c r="AC9" t="s">
         <v>135</v>
       </c>
-      <c r="AC9" t="s">
-        <v>136</v>
-      </c>
       <c r="AD9" t="s">
         <v>30</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>30</v>
       </c>
       <c r="AF9" t="s">
-        <v>164</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -3123,10 +3123,10 @@
         <v>165</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="C10" s="1">
-        <v>46234.29166666667</v>
+        <v>46245.29166666667</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -3138,10 +3138,10 @@
         <v>30</v>
       </c>
       <c r="G10" t="s">
+        <v>144</v>
+      </c>
+      <c r="H10" t="s">
         <v>130</v>
-      </c>
-      <c r="H10" t="s">
-        <v>131</v>
       </c>
       <c r="I10" t="s">
         <v>30</v>
@@ -3150,61 +3150,61 @@
         <v>167</v>
       </c>
       <c r="K10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10">
         <v>0</v>
       </c>
       <c r="O10">
-        <v>600</v>
+        <v>780</v>
       </c>
       <c r="P10">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="Q10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S10">
         <v>4</v>
       </c>
       <c r="T10">
-        <v>4</v>
-      </c>
-      <c r="U10">
-        <v>5</v>
-      </c>
-      <c r="V10" t="s">
-        <v>30</v>
+        <v>3</v>
+      </c>
+      <c r="U10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V10">
+        <v>3</v>
       </c>
       <c r="W10">
         <v>4</v>
       </c>
       <c r="X10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z10" t="s">
         <v>133</v>
       </c>
-      <c r="Y10" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z10" t="s">
+      <c r="AA10">
+        <v>2</v>
+      </c>
+      <c r="AB10" t="s">
         <v>134</v>
       </c>
-      <c r="AA10">
-        <v>3</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>135</v>
-      </c>
       <c r="AC10" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="AD10" t="s">
         <v>30</v>
@@ -3221,88 +3221,88 @@
         <v>169</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C11" s="1">
-        <v>46241.29166666667</v>
+        <v>46248.29166666667</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="F11" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="G11" t="s">
+        <v>144</v>
+      </c>
+      <c r="H11" t="s">
+        <v>134</v>
+      </c>
+      <c r="I11" t="s">
         <v>171</v>
-      </c>
-      <c r="H11" t="s">
-        <v>131</v>
-      </c>
-      <c r="I11" t="s">
-        <v>30</v>
       </c>
       <c r="J11" t="s">
         <v>172</v>
       </c>
       <c r="K11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>1500</v>
-      </c>
-      <c r="P11">
-        <v>210</v>
+        <v>240</v>
+      </c>
+      <c r="P11" t="s">
+        <v>30</v>
       </c>
       <c r="Q11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R11">
-        <v>5</v>
-      </c>
-      <c r="S11">
         <v>4</v>
       </c>
-      <c r="T11">
-        <v>5</v>
+      <c r="S11" t="s">
+        <v>30</v>
+      </c>
+      <c r="T11" t="s">
+        <v>30</v>
       </c>
       <c r="U11">
         <v>4</v>
       </c>
-      <c r="V11">
-        <v>4</v>
-      </c>
-      <c r="W11">
-        <v>5</v>
+      <c r="V11" t="s">
+        <v>30</v>
+      </c>
+      <c r="W11" t="s">
+        <v>30</v>
       </c>
       <c r="X11" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z11" t="s">
         <v>133</v>
       </c>
-      <c r="Y11" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>134</v>
-      </c>
-      <c r="AA11">
-        <v>3</v>
+      <c r="AA11" t="s">
+        <v>30</v>
       </c>
       <c r="AB11" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC11" t="s">
         <v>135</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>136</v>
       </c>
       <c r="AD11" t="s">
         <v>30</v>
@@ -3407,13 +3407,13 @@
         <v>190</v>
       </c>
       <c r="B2" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D2" s="1">
-        <v>46230.29166666667</v>
+        <v>46234.29166666667</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -3431,10 +3431,10 @@
         <v>193</v>
       </c>
       <c r="J2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" t="s">
         <v>194</v>
-      </c>
-      <c r="K2" t="s">
-        <v>195</v>
       </c>
       <c r="L2" t="s">
         <v>30</v>
@@ -3449,24 +3449,24 @@
         <v>30</v>
       </c>
       <c r="P2" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="Q2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="R2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="S2" t="s">
-        <v>197</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C3" t="s">
         <v>91</v>
@@ -3475,7 +3475,7 @@
         <v>46216.29166666667</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="s">
         <v>191</v>
@@ -3484,16 +3484,16 @@
         <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J3" t="s">
         <v>30</v>
       </c>
       <c r="K3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L3" t="s">
         <v>30</v>
@@ -3511,10 +3511,10 @@
         <v>32</v>
       </c>
       <c r="Q3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R3" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="S3" t="s">
         <v>30</v>
@@ -3522,10 +3522,10 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B4" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="C4" t="s">
         <v>52</v>
@@ -3534,7 +3534,7 @@
         <v>46241.29166666667</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F4" t="s">
         <v>191</v>
@@ -3543,16 +3543,16 @@
         <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="J4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="K4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L4" t="s">
         <v>30</v>
@@ -3570,30 +3570,30 @@
         <v>56</v>
       </c>
       <c r="Q4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R4" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="S4" t="s">
-        <v>207</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B5" t="s">
         <v>157</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="D5" s="1">
-        <v>46245.29166666667</v>
+        <v>46238.29166666667</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="s">
         <v>191</v>
@@ -3602,57 +3602,57 @@
         <v>30</v>
       </c>
       <c r="H5" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="I5" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="J5" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="K5" t="s">
+        <v>207</v>
+      </c>
+      <c r="L5" t="s">
+        <v>30</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
+      </c>
+      <c r="N5" t="s">
+        <v>30</v>
+      </c>
+      <c r="O5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P5" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>134</v>
+      </c>
+      <c r="R5" t="s">
         <v>195</v>
       </c>
-      <c r="L5" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5">
-        <v>4</v>
-      </c>
-      <c r="N5" t="s">
-        <v>30</v>
-      </c>
-      <c r="O5" t="s">
-        <v>30</v>
-      </c>
-      <c r="P5" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>131</v>
-      </c>
-      <c r="R5" t="s">
-        <v>206</v>
-      </c>
       <c r="S5" t="s">
-        <v>212</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B6" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="D6" s="1">
-        <v>46216.29166666667</v>
+        <v>46241.29166666667</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6" t="s">
         <v>191</v>
@@ -3661,37 +3661,37 @@
         <v>30</v>
       </c>
       <c r="H6" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="I6" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="J6" t="s">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="K6" t="s">
+        <v>194</v>
+      </c>
+      <c r="L6" t="s">
+        <v>30</v>
+      </c>
+      <c r="M6" t="s">
+        <v>30</v>
+      </c>
+      <c r="N6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>130</v>
+      </c>
+      <c r="R6" t="s">
         <v>195</v>
-      </c>
-      <c r="L6" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6" t="s">
-        <v>30</v>
-      </c>
-      <c r="N6" t="s">
-        <v>30</v>
-      </c>
-      <c r="O6" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>131</v>
-      </c>
-      <c r="R6" t="s">
-        <v>201</v>
       </c>
       <c r="S6" t="s">
         <v>30</v>
@@ -3699,19 +3699,19 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B7" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D7" s="1">
-        <v>46216.29166666667</v>
+        <v>46223.29166666667</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" t="s">
         <v>191</v>
@@ -3720,37 +3720,37 @@
         <v>30</v>
       </c>
       <c r="H7" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="I7" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="J7" t="s">
-        <v>30</v>
+        <v>206</v>
       </c>
       <c r="K7" t="s">
+        <v>194</v>
+      </c>
+      <c r="L7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M7">
+        <v>3</v>
+      </c>
+      <c r="N7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O7" t="s">
+        <v>30</v>
+      </c>
+      <c r="P7" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>130</v>
+      </c>
+      <c r="R7" t="s">
         <v>195</v>
-      </c>
-      <c r="L7" t="s">
-        <v>30</v>
-      </c>
-      <c r="M7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P7" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>131</v>
-      </c>
-      <c r="R7" t="s">
-        <v>201</v>
       </c>
       <c r="S7" t="s">
         <v>30</v>
@@ -3758,19 +3758,19 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B8" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="D8" s="1">
-        <v>46241.29166666667</v>
+        <v>46234.29166666667</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F8" t="s">
         <v>191</v>
@@ -3779,22 +3779,22 @@
         <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="I8" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="J8" t="s">
-        <v>221</v>
+        <v>30</v>
       </c>
       <c r="K8" t="s">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="L8" t="s">
         <v>30</v>
       </c>
-      <c r="M8">
-        <v>3</v>
+      <c r="M8" t="s">
+        <v>30</v>
       </c>
       <c r="N8" t="s">
         <v>30</v>
@@ -3803,33 +3803,33 @@
         <v>30</v>
       </c>
       <c r="P8" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="Q8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R8" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="S8" t="s">
-        <v>223</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D9" s="1">
-        <v>46223.29166666667</v>
+        <v>46216.29166666667</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9" t="s">
         <v>191</v>
@@ -3838,22 +3838,22 @@
         <v>30</v>
       </c>
       <c r="H9" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="I9" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="J9" t="s">
-        <v>221</v>
+        <v>30</v>
       </c>
       <c r="K9" t="s">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="L9" t="s">
         <v>30</v>
       </c>
-      <c r="M9">
-        <v>4</v>
+      <c r="M9" t="s">
+        <v>30</v>
       </c>
       <c r="N9" t="s">
         <v>30</v>
@@ -3862,13 +3862,13 @@
         <v>30</v>
       </c>
       <c r="P9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Q9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R9" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="S9" t="s">
         <v>30</v>
@@ -3876,19 +3876,19 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="B10" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="D10" s="1">
-        <v>46234.29166666667</v>
+        <v>46216.29166666667</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
         <v>191</v>
@@ -3897,57 +3897,57 @@
         <v>30</v>
       </c>
       <c r="H10" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="I10" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="J10" t="s">
         <v>30</v>
       </c>
       <c r="K10" t="s">
+        <v>194</v>
+      </c>
+      <c r="L10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M10" t="s">
+        <v>30</v>
+      </c>
+      <c r="N10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O10" t="s">
+        <v>30</v>
+      </c>
+      <c r="P10" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>130</v>
+      </c>
+      <c r="R10" t="s">
         <v>195</v>
       </c>
-      <c r="L10" t="s">
-        <v>30</v>
-      </c>
-      <c r="M10" t="s">
-        <v>30</v>
-      </c>
-      <c r="N10" t="s">
-        <v>30</v>
-      </c>
-      <c r="O10" t="s">
-        <v>30</v>
-      </c>
-      <c r="P10" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>131</v>
-      </c>
-      <c r="R10" t="s">
-        <v>230</v>
-      </c>
       <c r="S10" t="s">
-        <v>231</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="B11" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="D11" s="1">
-        <v>46234.29166666667</v>
+        <v>46216.29166666667</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
         <v>191</v>
@@ -3956,37 +3956,37 @@
         <v>30</v>
       </c>
       <c r="H11" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="I11" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="J11" t="s">
         <v>30</v>
       </c>
       <c r="K11" t="s">
+        <v>194</v>
+      </c>
+      <c r="L11" t="s">
+        <v>30</v>
+      </c>
+      <c r="M11" t="s">
+        <v>30</v>
+      </c>
+      <c r="N11" t="s">
+        <v>30</v>
+      </c>
+      <c r="O11" t="s">
+        <v>30</v>
+      </c>
+      <c r="P11" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>130</v>
+      </c>
+      <c r="R11" t="s">
         <v>195</v>
-      </c>
-      <c r="L11" t="s">
-        <v>30</v>
-      </c>
-      <c r="M11" t="s">
-        <v>30</v>
-      </c>
-      <c r="N11" t="s">
-        <v>30</v>
-      </c>
-      <c r="O11" t="s">
-        <v>30</v>
-      </c>
-      <c r="P11" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>131</v>
-      </c>
-      <c r="R11" t="s">
-        <v>201</v>
       </c>
       <c r="S11" t="s">
         <v>30</v>
@@ -3994,16 +3994,16 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="B12" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="D12" s="1">
-        <v>46223.29166666667</v>
+        <v>46245.29166666667</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -4015,22 +4015,22 @@
         <v>30</v>
       </c>
       <c r="H12" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="I12" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="J12" t="s">
-        <v>236</v>
+        <v>30</v>
       </c>
       <c r="K12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L12" t="s">
         <v>30</v>
       </c>
-      <c r="M12">
-        <v>5</v>
+      <c r="M12" t="s">
+        <v>30</v>
       </c>
       <c r="N12" t="s">
         <v>30</v>
@@ -4042,10 +4042,10 @@
         <v>34</v>
       </c>
       <c r="Q12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R12" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="S12" t="s">
         <v>30</v>
@@ -4053,16 +4053,16 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="B13" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="D13" s="1">
-        <v>46248.29166666667</v>
+        <v>46241.29166666667</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -4074,37 +4074,37 @@
         <v>30</v>
       </c>
       <c r="H13" t="s">
-        <v>228</v>
+        <v>197</v>
       </c>
       <c r="I13" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="J13" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="K13" t="s">
+        <v>227</v>
+      </c>
+      <c r="L13" t="s">
+        <v>30</v>
+      </c>
+      <c r="M13" t="s">
+        <v>30</v>
+      </c>
+      <c r="N13" t="s">
+        <v>30</v>
+      </c>
+      <c r="O13" t="s">
+        <v>30</v>
+      </c>
+      <c r="P13" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>130</v>
+      </c>
+      <c r="R13" t="s">
         <v>195</v>
-      </c>
-      <c r="L13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M13" t="s">
-        <v>30</v>
-      </c>
-      <c r="N13" t="s">
-        <v>30</v>
-      </c>
-      <c r="O13" t="s">
-        <v>30</v>
-      </c>
-      <c r="P13" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>131</v>
-      </c>
-      <c r="R13" t="s">
-        <v>201</v>
       </c>
       <c r="S13" t="s">
         <v>30</v>
@@ -4112,19 +4112,19 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="B14" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="D14" s="1">
-        <v>46241.29166666667</v>
+        <v>46234.29166666667</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F14" t="s">
         <v>191</v>
@@ -4133,16 +4133,16 @@
         <v>30</v>
       </c>
       <c r="H14" t="s">
-        <v>228</v>
+        <v>197</v>
       </c>
       <c r="I14" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="J14" t="s">
-        <v>205</v>
+        <v>30</v>
       </c>
       <c r="K14" t="s">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="L14" t="s">
         <v>30</v>
@@ -4157,24 +4157,24 @@
         <v>30</v>
       </c>
       <c r="P14" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="Q14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R14" t="s">
-        <v>201</v>
+        <v>230</v>
       </c>
       <c r="S14" t="s">
-        <v>30</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="B15" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C15" t="s">
         <v>91</v>
@@ -4183,7 +4183,7 @@
         <v>46216.29166666667</v>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F15" t="s">
         <v>191</v>
@@ -4192,16 +4192,16 @@
         <v>30</v>
       </c>
       <c r="H15" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="I15" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="J15" t="s">
         <v>30</v>
       </c>
       <c r="K15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L15" t="s">
         <v>30</v>
@@ -4219,10 +4219,10 @@
         <v>32</v>
       </c>
       <c r="Q15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R15" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="S15" t="s">
         <v>30</v>
@@ -4230,19 +4230,19 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="B16" t="s">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="D16" s="1">
-        <v>46241.29166666667</v>
+        <v>46248.29166666667</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="s">
         <v>191</v>
@@ -4251,37 +4251,37 @@
         <v>30</v>
       </c>
       <c r="H16" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="I16" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="J16" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="K16" t="s">
+        <v>194</v>
+      </c>
+      <c r="L16" t="s">
+        <v>30</v>
+      </c>
+      <c r="M16" t="s">
+        <v>30</v>
+      </c>
+      <c r="N16" t="s">
+        <v>30</v>
+      </c>
+      <c r="O16" t="s">
+        <v>30</v>
+      </c>
+      <c r="P16" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>130</v>
+      </c>
+      <c r="R16" t="s">
         <v>195</v>
-      </c>
-      <c r="L16" t="s">
-        <v>30</v>
-      </c>
-      <c r="M16" t="s">
-        <v>30</v>
-      </c>
-      <c r="N16" t="s">
-        <v>30</v>
-      </c>
-      <c r="O16" t="s">
-        <v>30</v>
-      </c>
-      <c r="P16" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>131</v>
-      </c>
-      <c r="R16" t="s">
-        <v>201</v>
       </c>
       <c r="S16" t="s">
         <v>30</v>
@@ -4289,16 +4289,16 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="B17" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="D17" s="1">
-        <v>46234.29166666667</v>
+        <v>46248.29166666667</v>
       </c>
       <c r="E17">
         <v>2</v>
@@ -4310,22 +4310,22 @@
         <v>30</v>
       </c>
       <c r="H17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I17" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="J17" t="s">
-        <v>30</v>
+        <v>206</v>
       </c>
       <c r="K17" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L17" t="s">
         <v>30</v>
       </c>
       <c r="M17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N17" t="s">
         <v>30</v>
@@ -4337,30 +4337,30 @@
         <v>34</v>
       </c>
       <c r="Q17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R17" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="S17" t="s">
-        <v>30</v>
+        <v>238</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="B18" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D18" s="1">
-        <v>46234.29166666667</v>
+        <v>46241.29166666667</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
         <v>191</v>
@@ -4369,37 +4369,37 @@
         <v>30</v>
       </c>
       <c r="H18" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="I18" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="J18" t="s">
-        <v>30</v>
+        <v>241</v>
       </c>
       <c r="K18" t="s">
+        <v>194</v>
+      </c>
+      <c r="L18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M18" t="s">
+        <v>30</v>
+      </c>
+      <c r="N18" t="s">
+        <v>30</v>
+      </c>
+      <c r="O18" t="s">
+        <v>30</v>
+      </c>
+      <c r="P18" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>130</v>
+      </c>
+      <c r="R18" t="s">
         <v>195</v>
-      </c>
-      <c r="L18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M18" t="s">
-        <v>30</v>
-      </c>
-      <c r="N18" t="s">
-        <v>30</v>
-      </c>
-      <c r="O18" t="s">
-        <v>30</v>
-      </c>
-      <c r="P18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>131</v>
-      </c>
-      <c r="R18" t="s">
-        <v>201</v>
       </c>
       <c r="S18" t="s">
         <v>30</v>
@@ -4407,16 +4407,16 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="B19" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="D19" s="1">
-        <v>46245.29166666667</v>
+        <v>46223.29166666667</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -4428,22 +4428,22 @@
         <v>30</v>
       </c>
       <c r="H19" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="I19" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="J19" t="s">
-        <v>30</v>
+        <v>245</v>
       </c>
       <c r="K19" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="L19" t="s">
         <v>30</v>
       </c>
-      <c r="M19" t="s">
-        <v>30</v>
+      <c r="M19">
+        <v>4</v>
       </c>
       <c r="N19" t="s">
         <v>30</v>
@@ -4455,10 +4455,10 @@
         <v>34</v>
       </c>
       <c r="Q19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R19" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="S19" t="s">
         <v>30</v>
@@ -4466,10 +4466,10 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B20" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="C20" t="s">
         <v>25</v>
@@ -4487,16 +4487,16 @@
         <v>30</v>
       </c>
       <c r="H20" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="I20" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="J20" t="s">
         <v>30</v>
       </c>
       <c r="K20" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L20" t="s">
         <v>30</v>
@@ -4514,10 +4514,10 @@
         <v>34</v>
       </c>
       <c r="Q20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R20" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="S20" t="s">
         <v>30</v>
@@ -4525,19 +4525,19 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B21" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D21" s="1">
-        <v>46241.29166666667</v>
+        <v>46230.29166666667</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F21" t="s">
         <v>191</v>
@@ -4546,37 +4546,37 @@
         <v>30</v>
       </c>
       <c r="H21" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I21" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="J21" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="K21" t="s">
+        <v>227</v>
+      </c>
+      <c r="L21" t="s">
+        <v>30</v>
+      </c>
+      <c r="M21" t="s">
+        <v>30</v>
+      </c>
+      <c r="N21" t="s">
+        <v>30</v>
+      </c>
+      <c r="O21" t="s">
+        <v>30</v>
+      </c>
+      <c r="P21" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>134</v>
+      </c>
+      <c r="R21" t="s">
         <v>195</v>
-      </c>
-      <c r="L21" t="s">
-        <v>30</v>
-      </c>
-      <c r="M21" t="s">
-        <v>30</v>
-      </c>
-      <c r="N21" t="s">
-        <v>30</v>
-      </c>
-      <c r="O21" t="s">
-        <v>30</v>
-      </c>
-      <c r="P21" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>131</v>
-      </c>
-      <c r="R21" t="s">
-        <v>201</v>
       </c>
       <c r="S21" t="s">
         <v>30</v>
@@ -4584,16 +4584,16 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B22" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="D22" s="1">
-        <v>46241.29166666667</v>
+        <v>46216.29166666667</v>
       </c>
       <c r="E22">
         <v>3</v>
@@ -4605,37 +4605,37 @@
         <v>30</v>
       </c>
       <c r="H22" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="I22" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="J22" t="s">
-        <v>205</v>
+        <v>30</v>
       </c>
       <c r="K22" t="s">
+        <v>194</v>
+      </c>
+      <c r="L22" t="s">
+        <v>30</v>
+      </c>
+      <c r="M22" t="s">
+        <v>30</v>
+      </c>
+      <c r="N22" t="s">
+        <v>30</v>
+      </c>
+      <c r="O22" t="s">
+        <v>30</v>
+      </c>
+      <c r="P22" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>130</v>
+      </c>
+      <c r="R22" t="s">
         <v>195</v>
-      </c>
-      <c r="L22" t="s">
-        <v>30</v>
-      </c>
-      <c r="M22">
-        <v>4</v>
-      </c>
-      <c r="N22" t="s">
-        <v>30</v>
-      </c>
-      <c r="O22" t="s">
-        <v>30</v>
-      </c>
-      <c r="P22" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>131</v>
-      </c>
-      <c r="R22" t="s">
-        <v>201</v>
       </c>
       <c r="S22" t="s">
         <v>30</v>
@@ -4643,16 +4643,16 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C23" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="D23" s="1">
-        <v>46223.29166666667</v>
+        <v>46230.29166666667</v>
       </c>
       <c r="E23">
         <v>2</v>
@@ -4664,22 +4664,22 @@
         <v>30</v>
       </c>
       <c r="H23" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="I23" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="J23" t="s">
+        <v>206</v>
+      </c>
+      <c r="K23" t="s">
         <v>194</v>
       </c>
-      <c r="K23" t="s">
-        <v>195</v>
-      </c>
       <c r="L23" t="s">
         <v>30</v>
       </c>
       <c r="M23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N23" t="s">
         <v>30</v>
@@ -4688,33 +4688,33 @@
         <v>30</v>
       </c>
       <c r="P23" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="Q23" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="R23" t="s">
-        <v>201</v>
+        <v>254</v>
       </c>
       <c r="S23" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="D24" s="1">
-        <v>46230.29166666667</v>
+        <v>46241.29166666667</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F24" t="s">
         <v>191</v>
@@ -4723,40 +4723,40 @@
         <v>30</v>
       </c>
       <c r="H24" t="s">
-        <v>228</v>
+        <v>257</v>
       </c>
       <c r="I24" t="s">
+        <v>258</v>
+      </c>
+      <c r="J24" t="s">
+        <v>202</v>
+      </c>
+      <c r="K24" t="s">
+        <v>194</v>
+      </c>
+      <c r="L24" t="s">
+        <v>30</v>
+      </c>
+      <c r="M24">
+        <v>4</v>
+      </c>
+      <c r="N24" t="s">
+        <v>30</v>
+      </c>
+      <c r="O24" t="s">
+        <v>30</v>
+      </c>
+      <c r="P24" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>130</v>
+      </c>
+      <c r="R24" t="s">
+        <v>259</v>
+      </c>
+      <c r="S24" t="s">
         <v>260</v>
-      </c>
-      <c r="J24" t="s">
-        <v>194</v>
-      </c>
-      <c r="K24" t="s">
-        <v>222</v>
-      </c>
-      <c r="L24" t="s">
-        <v>30</v>
-      </c>
-      <c r="M24" t="s">
-        <v>30</v>
-      </c>
-      <c r="N24" t="s">
-        <v>30</v>
-      </c>
-      <c r="O24" t="s">
-        <v>30</v>
-      </c>
-      <c r="P24" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>135</v>
-      </c>
-      <c r="R24" t="s">
-        <v>201</v>
-      </c>
-      <c r="S24" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
@@ -4764,13 +4764,13 @@
         <v>261</v>
       </c>
       <c r="B25" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="D25" s="1">
-        <v>46245.29166666667</v>
+        <v>46223.29166666667</v>
       </c>
       <c r="E25">
         <v>3</v>
@@ -4782,22 +4782,22 @@
         <v>30</v>
       </c>
       <c r="H25" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I25" t="s">
         <v>262</v>
       </c>
       <c r="J25" t="s">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="K25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L25" t="s">
         <v>30</v>
       </c>
-      <c r="M25" t="s">
-        <v>30</v>
+      <c r="M25">
+        <v>5</v>
       </c>
       <c r="N25" t="s">
         <v>30</v>
@@ -4809,10 +4809,10 @@
         <v>34</v>
       </c>
       <c r="Q25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="R25" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="S25" t="s">
         <v>30</v>
@@ -4823,16 +4823,16 @@
         <v>263</v>
       </c>
       <c r="B26" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C26" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="D26" s="1">
-        <v>46216.29166666667</v>
+        <v>46241.29166666667</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F26" t="s">
         <v>191</v>
@@ -4841,57 +4841,57 @@
         <v>30</v>
       </c>
       <c r="H26" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="I26" t="s">
         <v>264</v>
       </c>
       <c r="J26" t="s">
-        <v>30</v>
+        <v>245</v>
       </c>
       <c r="K26" t="s">
+        <v>227</v>
+      </c>
+      <c r="L26" t="s">
+        <v>30</v>
+      </c>
+      <c r="M26">
+        <v>3</v>
+      </c>
+      <c r="N26" t="s">
+        <v>30</v>
+      </c>
+      <c r="O26" t="s">
+        <v>30</v>
+      </c>
+      <c r="P26" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>130</v>
+      </c>
+      <c r="R26" t="s">
         <v>195</v>
       </c>
-      <c r="L26" t="s">
-        <v>30</v>
-      </c>
-      <c r="M26" t="s">
-        <v>30</v>
-      </c>
-      <c r="N26" t="s">
-        <v>30</v>
-      </c>
-      <c r="O26" t="s">
-        <v>30</v>
-      </c>
-      <c r="P26" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>131</v>
-      </c>
-      <c r="R26" t="s">
-        <v>201</v>
-      </c>
       <c r="S26" t="s">
-        <v>30</v>
+        <v>265</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B27" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="C27" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="D27" s="1">
-        <v>46216.29166666667</v>
+        <v>46245.29166666667</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F27" t="s">
         <v>191</v>
@@ -4900,37 +4900,37 @@
         <v>30</v>
       </c>
       <c r="H27" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="I27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J27" t="s">
         <v>30</v>
       </c>
       <c r="K27" t="s">
+        <v>227</v>
+      </c>
+      <c r="L27" t="s">
+        <v>30</v>
+      </c>
+      <c r="M27" t="s">
+        <v>30</v>
+      </c>
+      <c r="N27" t="s">
+        <v>30</v>
+      </c>
+      <c r="O27" t="s">
+        <v>30</v>
+      </c>
+      <c r="P27" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>130</v>
+      </c>
+      <c r="R27" t="s">
         <v>195</v>
-      </c>
-      <c r="L27" t="s">
-        <v>30</v>
-      </c>
-      <c r="M27" t="s">
-        <v>30</v>
-      </c>
-      <c r="N27" t="s">
-        <v>30</v>
-      </c>
-      <c r="O27" t="s">
-        <v>30</v>
-      </c>
-      <c r="P27" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>131</v>
-      </c>
-      <c r="R27" t="s">
-        <v>201</v>
       </c>
       <c r="S27" t="s">
         <v>30</v>
@@ -4938,16 +4938,16 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B28" t="s">
-        <v>127</v>
+        <v>157</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="D28" s="1">
-        <v>46248.29166666667</v>
+        <v>46238.29166666667</v>
       </c>
       <c r="E28">
         <v>2</v>
@@ -4959,40 +4959,40 @@
         <v>30</v>
       </c>
       <c r="H28" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="I28" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J28" t="s">
-        <v>194</v>
+        <v>241</v>
       </c>
       <c r="K28" t="s">
+        <v>227</v>
+      </c>
+      <c r="L28" t="s">
+        <v>30</v>
+      </c>
+      <c r="M28" t="s">
+        <v>30</v>
+      </c>
+      <c r="N28" t="s">
+        <v>30</v>
+      </c>
+      <c r="O28" t="s">
+        <v>30</v>
+      </c>
+      <c r="P28" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>134</v>
+      </c>
+      <c r="R28" t="s">
         <v>195</v>
       </c>
-      <c r="L28" t="s">
-        <v>30</v>
-      </c>
-      <c r="M28">
-        <v>5</v>
-      </c>
-      <c r="N28" t="s">
-        <v>30</v>
-      </c>
-      <c r="O28" t="s">
-        <v>30</v>
-      </c>
-      <c r="P28" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>131</v>
-      </c>
-      <c r="R28" t="s">
-        <v>201</v>
-      </c>
       <c r="S28" t="s">
-        <v>269</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
@@ -5000,16 +5000,16 @@
         <v>270</v>
       </c>
       <c r="B29" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C29" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="D29" s="1">
-        <v>46238.29166666667</v>
+        <v>46245.29166666667</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="s">
         <v>191</v>
@@ -5018,40 +5018,40 @@
         <v>30</v>
       </c>
       <c r="H29" t="s">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="I29" t="s">
         <v>271</v>
       </c>
       <c r="J29" t="s">
+        <v>241</v>
+      </c>
+      <c r="K29" t="s">
         <v>194</v>
       </c>
-      <c r="K29" t="s">
+      <c r="L29" t="s">
+        <v>30</v>
+      </c>
+      <c r="M29">
+        <v>4</v>
+      </c>
+      <c r="N29" t="s">
+        <v>30</v>
+      </c>
+      <c r="O29" t="s">
+        <v>30</v>
+      </c>
+      <c r="P29" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>130</v>
+      </c>
+      <c r="R29" t="s">
+        <v>259</v>
+      </c>
+      <c r="S29" t="s">
         <v>272</v>
-      </c>
-      <c r="L29" t="s">
-        <v>30</v>
-      </c>
-      <c r="M29">
-        <v>5</v>
-      </c>
-      <c r="N29" t="s">
-        <v>30</v>
-      </c>
-      <c r="O29" t="s">
-        <v>30</v>
-      </c>
-      <c r="P29" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>135</v>
-      </c>
-      <c r="R29" t="s">
-        <v>201</v>
-      </c>
-      <c r="S29" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
@@ -5059,16 +5059,16 @@
         <v>273</v>
       </c>
       <c r="B30" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="C30" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D30" s="1">
-        <v>46238.29166666667</v>
+        <v>46234.29166666667</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" t="s">
         <v>191</v>
@@ -5077,16 +5077,16 @@
         <v>30</v>
       </c>
       <c r="H30" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="I30" t="s">
         <v>274</v>
       </c>
       <c r="J30" t="s">
-        <v>211</v>
+        <v>30</v>
       </c>
       <c r="K30" t="s">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="L30" t="s">
         <v>30</v>
@@ -5101,13 +5101,13 @@
         <v>30</v>
       </c>
       <c r="P30" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q30" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="R30" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="S30" t="s">
         <v>30</v>
@@ -5174,819 +5174,819 @@
         <v>128</v>
       </c>
       <c r="E2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F2" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G2" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="H2" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C3" s="1">
-        <v>46248.29166666667</v>
+        <v>46241.29166666667</v>
       </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E3" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G3" t="s">
         <v>201</v>
       </c>
-      <c r="G3" t="s">
-        <v>268</v>
-      </c>
       <c r="H3" t="s">
-        <v>267</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="1">
+        <v>46241.29166666667</v>
+      </c>
+      <c r="D4" t="s">
         <v>137</v>
-      </c>
-      <c r="C4" s="1">
-        <v>46230.29166666667</v>
-      </c>
-      <c r="D4" t="s">
-        <v>138</v>
       </c>
       <c r="E4" t="s">
         <v>139</v>
       </c>
       <c r="F4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G4" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="H4" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="B5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C5" s="1">
+        <v>46241.29166666667</v>
+      </c>
+      <c r="D5" t="s">
         <v>137</v>
-      </c>
-      <c r="C5" s="1">
-        <v>46230.29166666667</v>
-      </c>
-      <c r="D5" t="s">
-        <v>138</v>
       </c>
       <c r="E5" t="s">
         <v>139</v>
       </c>
       <c r="F5" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G5" t="s">
-        <v>260</v>
+        <v>226</v>
       </c>
       <c r="H5" t="s">
-        <v>259</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C6" s="1">
-        <v>46248.29166666667</v>
+        <v>46241.29166666667</v>
       </c>
       <c r="D6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E6" t="s">
         <v>139</v>
       </c>
       <c r="F6" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G6" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="H6" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C7" s="1">
-        <v>46216.29166666667</v>
+        <v>46241.29166666667</v>
       </c>
       <c r="D7" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E7" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F7" t="s">
-        <v>201</v>
+        <v>259</v>
       </c>
       <c r="G7" t="s">
-        <v>200</v>
+        <v>258</v>
       </c>
       <c r="H7" t="s">
-        <v>198</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C8" s="1">
-        <v>46216.29166666667</v>
+        <v>46241.29166666667</v>
       </c>
       <c r="D8" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E8" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F8" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G8" t="s">
-        <v>214</v>
+        <v>264</v>
       </c>
       <c r="H8" t="s">
-        <v>213</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C9" s="1">
-        <v>46216.29166666667</v>
+        <v>46241.29166666667</v>
       </c>
       <c r="D9" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E9" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F9" t="s">
-        <v>201</v>
+        <v>278</v>
       </c>
       <c r="G9" t="s">
-        <v>217</v>
+        <v>279</v>
       </c>
       <c r="H9" t="s">
-        <v>215</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="B10" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C10" s="1">
-        <v>46216.29166666667</v>
+        <v>46234.29166666667</v>
       </c>
       <c r="D10" t="s">
+        <v>143</v>
+      </c>
+      <c r="E10" t="s">
         <v>144</v>
       </c>
-      <c r="E10" t="s">
-        <v>130</v>
-      </c>
       <c r="F10" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G10" t="s">
-        <v>242</v>
+        <v>193</v>
       </c>
       <c r="H10" t="s">
-        <v>241</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="B11" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C11" s="1">
-        <v>46216.29166666667</v>
+        <v>46234.29166666667</v>
       </c>
       <c r="D11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E11" t="s">
         <v>144</v>
       </c>
-      <c r="E11" t="s">
-        <v>130</v>
-      </c>
       <c r="F11" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G11" t="s">
-        <v>264</v>
+        <v>214</v>
       </c>
       <c r="H11" t="s">
-        <v>263</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="B12" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C12" s="1">
-        <v>46216.29166666667</v>
+        <v>46234.29166666667</v>
       </c>
       <c r="D12" t="s">
+        <v>143</v>
+      </c>
+      <c r="E12" t="s">
         <v>144</v>
       </c>
-      <c r="E12" t="s">
-        <v>130</v>
-      </c>
       <c r="F12" t="s">
-        <v>201</v>
+        <v>230</v>
       </c>
       <c r="G12" t="s">
-        <v>266</v>
+        <v>229</v>
       </c>
       <c r="H12" t="s">
-        <v>265</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="B13" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C13" s="1">
-        <v>46248.29166666667</v>
+        <v>46234.29166666667</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E13" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="F13" t="s">
-        <v>278</v>
+        <v>195</v>
       </c>
       <c r="G13" t="s">
-        <v>151</v>
+        <v>274</v>
       </c>
       <c r="H13" t="s">
-        <v>30</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C14" s="1">
-        <v>46223.29166666667</v>
+        <v>46248.29166666667</v>
       </c>
       <c r="D14" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="E14" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="F14" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G14" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="H14" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C15" s="1">
-        <v>46223.29166666667</v>
+        <v>46248.29166666667</v>
       </c>
       <c r="D15" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="E15" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="F15" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G15" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H15" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C16" s="1">
-        <v>46223.29166666667</v>
+        <v>46216.29166666667</v>
       </c>
       <c r="D16" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="E16" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="F16" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G16" t="s">
-        <v>258</v>
+        <v>198</v>
       </c>
       <c r="H16" t="s">
-        <v>257</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B17" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C17" s="1">
-        <v>46223.29166666667</v>
+        <v>46216.29166666667</v>
       </c>
       <c r="D17" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="E17" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="F17" t="s">
-        <v>279</v>
+        <v>195</v>
       </c>
       <c r="G17" t="s">
-        <v>280</v>
+        <v>216</v>
       </c>
       <c r="H17" t="s">
-        <v>30</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="B18" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C18" s="1">
-        <v>46245.29166666667</v>
+        <v>46216.29166666667</v>
       </c>
       <c r="D18" t="s">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="E18" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="F18" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="G18" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="H18" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="B19" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C19" s="1">
-        <v>46245.29166666667</v>
+        <v>46216.29166666667</v>
       </c>
       <c r="D19" t="s">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="E19" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="F19" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G19" t="s">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="H19" t="s">
-        <v>249</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="B20" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C20" s="1">
-        <v>46245.29166666667</v>
+        <v>46216.29166666667</v>
       </c>
       <c r="D20" t="s">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="E20" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="F20" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G20" t="s">
-        <v>262</v>
+        <v>233</v>
       </c>
       <c r="H20" t="s">
-        <v>261</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="B21" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="C21" s="1">
-        <v>46238.29166666667</v>
+        <v>46216.29166666667</v>
       </c>
       <c r="D21" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="E21" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="F21" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G21" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="H21" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B22" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C22" s="1">
-        <v>46238.29166666667</v>
+        <v>46230.29166666667</v>
       </c>
       <c r="D22" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="E22" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="F22" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G22" t="s">
-        <v>274</v>
+        <v>249</v>
       </c>
       <c r="H22" t="s">
-        <v>273</v>
+        <v>248</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B23" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C23" s="1">
-        <v>46234.29166666667</v>
+        <v>46230.29166666667</v>
       </c>
       <c r="D23" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="E23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F23" t="s">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="G23" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="H23" t="s">
-        <v>227</v>
+        <v>252</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B24" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C24" s="1">
-        <v>46234.29166666667</v>
+        <v>46238.29166666667</v>
       </c>
       <c r="D24" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="E24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F24" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G24" t="s">
-        <v>233</v>
+        <v>205</v>
       </c>
       <c r="H24" t="s">
-        <v>232</v>
+        <v>203</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B25" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C25" s="1">
-        <v>46234.29166666667</v>
+        <v>46238.29166666667</v>
       </c>
       <c r="D25" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="E25" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F25" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G25" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="H25" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="B26" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C26" s="1">
-        <v>46234.29166666667</v>
+        <v>46223.29166666667</v>
       </c>
       <c r="D26" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E26" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="F26" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G26" t="s">
-        <v>248</v>
+        <v>212</v>
       </c>
       <c r="H26" t="s">
-        <v>247</v>
+        <v>211</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="B27" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C27" s="1">
-        <v>46241.29166666667</v>
+        <v>46223.29166666667</v>
       </c>
       <c r="D27" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="E27" t="s">
-        <v>171</v>
+        <v>144</v>
       </c>
       <c r="F27" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="G27" t="s">
-        <v>204</v>
+        <v>244</v>
       </c>
       <c r="H27" t="s">
-        <v>202</v>
+        <v>242</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="B28" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C28" s="1">
-        <v>46241.29166666667</v>
+        <v>46223.29166666667</v>
       </c>
       <c r="D28" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="E28" t="s">
-        <v>171</v>
+        <v>144</v>
       </c>
       <c r="F28" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G28" t="s">
-        <v>220</v>
+        <v>262</v>
       </c>
       <c r="H28" t="s">
-        <v>218</v>
+        <v>261</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="B29" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C29" s="1">
-        <v>46241.29166666667</v>
+        <v>46223.29166666667</v>
       </c>
       <c r="D29" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="E29" t="s">
-        <v>171</v>
+        <v>144</v>
       </c>
       <c r="F29" t="s">
-        <v>201</v>
+        <v>278</v>
       </c>
       <c r="G29" t="s">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="H29" t="s">
-        <v>239</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C30" s="1">
-        <v>46241.29166666667</v>
+        <v>46245.29166666667</v>
       </c>
       <c r="D30" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="E30" t="s">
-        <v>171</v>
+        <v>144</v>
       </c>
       <c r="F30" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G30" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="H30" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C31" s="1">
-        <v>46241.29166666667</v>
+        <v>46245.29166666667</v>
       </c>
       <c r="D31" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="E31" t="s">
-        <v>171</v>
+        <v>144</v>
       </c>
       <c r="F31" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="G31" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="H31" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B32" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C32" s="1">
-        <v>46241.29166666667</v>
+        <v>46245.29166666667</v>
       </c>
       <c r="D32" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="E32" t="s">
-        <v>171</v>
+        <v>144</v>
       </c>
       <c r="F32" t="s">
-        <v>201</v>
+        <v>259</v>
       </c>
       <c r="G32" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="H32" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="B33" t="s">
         <v>169</v>
       </c>
       <c r="C33" s="1">
-        <v>46241.29166666667</v>
+        <v>46248.29166666667</v>
       </c>
       <c r="D33" t="s">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="E33" t="s">
-        <v>171</v>
+        <v>144</v>
       </c>
       <c r="F33" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G33" t="s">
-        <v>281</v>
+        <v>172</v>
       </c>
       <c r="H33" t="s">
         <v>30</v>
@@ -6212,18 +6212,18 @@
         <v>318</v>
       </c>
       <c r="B20" t="s">
+        <v>316</v>
+      </c>
+      <c r="C20" t="s">
         <v>319</v>
-      </c>
-      <c r="C20" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>320</v>
+      </c>
+      <c r="B21" t="s">
         <v>321</v>
-      </c>
-      <c r="B21" t="s">
-        <v>316</v>
       </c>
       <c r="C21" t="s">
         <v>322</v>
@@ -6234,7 +6234,7 @@
         <v>323</v>
       </c>
       <c r="B22" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C22" t="s">
         <v>324</v>
@@ -6245,7 +6245,7 @@
         <v>325</v>
       </c>
       <c r="B23" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C23" t="s">
         <v>326</v>
@@ -6256,7 +6256,7 @@
         <v>327</v>
       </c>
       <c r="B24" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C24" t="s">
         <v>328</v>
@@ -6267,7 +6267,7 @@
         <v>329</v>
       </c>
       <c r="B25" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C25" t="s">
         <v>330</v>
@@ -6278,7 +6278,7 @@
         <v>331</v>
       </c>
       <c r="B26" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C26" t="s">
         <v>332</v>
